--- a/.design/DB/DB設計たたき台.xlsx
+++ b/.design/DB/DB設計たたき台.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProjects\vtuber-meikan\.design\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/segar/Documents/GitHub/vtuber-meikan/.design/DB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B5CC9-91B3-4C79-8A3D-D625C43563D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8D3175-8902-6C4D-A1DE-DD2B50478AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="-120" windowWidth="57840" windowHeight="31920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">テーブル一覧!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テーブル定義_一覧!$A$1:$U$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テーブル定義_一覧!$A$1:$U$271</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">型とバイト数!$A$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="523">
   <si>
     <t>設計完了</t>
   </si>
@@ -879,27 +879,6 @@
   </si>
   <si>
     <t>動画URL</t>
-  </si>
-  <si>
-    <t>relation</t>
-  </si>
-  <si>
-    <t>関係値</t>
-  </si>
-  <si>
-    <t>ノード元</t>
-  </si>
-  <si>
-    <t>node_to</t>
-  </si>
-  <si>
-    <t>ノード先</t>
-  </si>
-  <si>
-    <t>node_name</t>
-  </si>
-  <si>
-    <t>関係名</t>
   </si>
   <si>
     <t>https://qiita.com/hk_arc/items/0474d28bc8620571db3c</t>
@@ -1437,28 +1416,6 @@
       <t>ドウガ</t>
     </rPh>
     <rPh sb="16" eb="18">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>相関図に使用するプロフィール間の関係値（ノード）を管理する</t>
-    <rPh sb="0" eb="3">
-      <t>ソウカンズ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カンケイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
       <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="3"/>
@@ -1574,14 +1531,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>node_from</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>node_from + node_to で UNIQUEにする</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>格納サイズ(byte)</t>
   </si>
   <si>
@@ -1842,7 +1791,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2005,7 +1954,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2060,16 +2009,10 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2287,20 +2230,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="3.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="110.7109375" customWidth="1"/>
-    <col min="8" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="3.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="110.6640625" customWidth="1"/>
+    <col min="8" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,17 +2269,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1">
       <c r="A2" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C2,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
       </c>
       <c r="B2" s="2">
-        <f t="shared" ref="B2:B29" si="0">ROW()-1</f>
+        <f t="shared" ref="B2:B28" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="C2" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="C2:C29" ca="1">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル定義_一覧!D:D,(テーブル定義_一覧!D:D&lt;&gt;"")*(テーブル定義_一覧!D:D&lt;&gt;"テーブル名(物理名)")))</f>
+        <f t="array" aca="1" ref="C2:C28" ca="1">_xlfn.UNIQUE(_xlfn._xlws.FILTER(テーブル定義_一覧!D:D,(テーブル定義_一覧!D:D&lt;&gt;"")*(テーブル定義_一覧!D:D&lt;&gt;"テーブル名(物理名)")))</f>
         <v>vtuber_profiles</v>
       </c>
       <c r="D2" s="3" t="str">
@@ -2351,11 +2294,11 @@
         <v>8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C3,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2384,7 +2327,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C4,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2413,7 +2356,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C5,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2442,7 +2385,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1">
       <c r="A6" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C6,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2471,7 +2414,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1">
       <c r="A7" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C7,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2500,7 +2443,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1">
       <c r="A8" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C8,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2529,7 +2472,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1">
       <c r="A9" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C9,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2558,7 +2501,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1">
       <c r="A10" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C10,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2587,7 +2530,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1">
       <c r="A11" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C11,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2616,7 +2559,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1">
       <c r="A12" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C12,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2645,7 +2588,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1">
       <c r="A13" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C13,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2674,7 +2617,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1">
       <c r="A14" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C14,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v/>
@@ -2703,7 +2646,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1">
       <c r="A15" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C15,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2732,7 +2675,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1">
       <c r="A16" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C16,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2761,7 +2704,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1">
       <c r="A17" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C17,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2790,7 +2733,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1">
       <c r="A18" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C18,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2819,7 +2762,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1">
       <c r="A19" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C19,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2848,7 +2791,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1">
       <c r="A20" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C20,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2877,7 +2820,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1">
       <c r="A21" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C21,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2906,7 +2849,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1">
       <c r="A22" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C22,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2935,7 +2878,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1">
       <c r="A23" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C23,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2964,7 +2907,7 @@
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1">
       <c r="A24" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C24,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -2989,11 +2932,11 @@
         <v>8</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1">
       <c r="A25" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C25,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -3018,11 +2961,11 @@
         <v>8</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1">
       <c r="A26" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C26,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -3033,25 +2976,25 @@
       </c>
       <c r="C26" s="6" t="str">
         <f ca="1"/>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="D26" s="3" t="str">
         <f ca="1">_xlfn.XLOOKUP(C26,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="E26" s="6">
         <f ca="1">SUMIF(テーブル定義_一覧!D:D,C26,テーブル定義_一覧!I:I)</f>
-        <v>1288</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>6152</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>456</v>
+      <c r="G26" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1">
       <c r="A27" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C27,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -3062,25 +3005,25 @@
       </c>
       <c r="C27" s="8" t="str">
         <f ca="1"/>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="D27" s="5" t="str">
         <f ca="1">_xlfn.XLOOKUP(C27,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="E27" s="8">
         <f ca="1">SUMIF(テーブル定義_一覧!D:D,C27,テーブル定義_一覧!I:I)</f>
-        <v>6152</v>
-      </c>
-      <c r="F27" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>463</v>
+      <c r="G27" s="6" t="s">
+        <v>461</v>
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18">
       <c r="A28" s="1" t="str">
         <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C28,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
         <v>〇</v>
@@ -3091,11 +3034,11 @@
       </c>
       <c r="C28" s="6" t="str">
         <f ca="1"/>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="D28" s="6" t="str">
         <f ca="1">_xlfn.XLOOKUP(C28,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="E28" s="6">
         <f ca="1">SUMIF(テーブル定義_一覧!D:D,C28,テーブル定義_一覧!I:I)</f>
@@ -3105,38 +3048,9 @@
         <v>8</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="H28" s="6"/>
-    </row>
-    <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="str">
-        <f ca="1">IF(COUNTIFS(テーブル定義_一覧!$D:$D,$C29,テーブル定義_一覧!$A:$A,"")&gt;0,"","〇")</f>
-        <v>〇</v>
-      </c>
-      <c r="B29" s="4">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C29" s="18" t="str">
-        <f ca="1"/>
-        <v>profile_activity</v>
-      </c>
-      <c r="D29" s="6" t="str">
-        <f ca="1">_xlfn.XLOOKUP(C29,テーブル定義_一覧!D:D,テーブル定義_一覧!E:E,"error")</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="E29" s="6">
-        <f ca="1">SUMIF(テーブル定義_一覧!D:D,C29,テーブル定義_一覧!I:I)</f>
-        <v>1032</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="H29" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -3148,32 +3062,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U280"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U271"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" style="7" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="4.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4" style="7" customWidth="1"/>
-    <col min="11" max="11" width="3.85546875" style="7" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="7.7109375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="31.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.83203125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="7" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="8.5" style="7" customWidth="1"/>
+    <col min="15" max="15" width="7.6640625" style="7" customWidth="1"/>
+    <col min="16" max="16" width="31.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="13" style="7" customWidth="1"/>
-    <col min="21" max="21" width="84.42578125" style="7" customWidth="1"/>
-    <col min="22" max="16384" width="14.42578125" style="7"/>
+    <col min="21" max="21" width="84.5" style="7" customWidth="1"/>
+    <col min="22" max="16384" width="14.5" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3238,7 +3152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="18.75" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
@@ -3261,7 +3175,7 @@
         <v>vtuber_profiles_uuid</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>49</v>
@@ -3283,7 +3197,7 @@
         <v>128</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K2" s="11"/>
       <c r="L2" s="9"/>
@@ -3292,10 +3206,10 @@
         <v/>
       </c>
       <c r="N2" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P2" s="11" t="s">
         <v>52</v>
@@ -3306,7 +3220,7 @@
       <c r="T2" s="9"/>
       <c r="U2" s="11"/>
     </row>
-    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>46</v>
       </c>
@@ -3359,10 +3273,10 @@
         <v/>
       </c>
       <c r="N3" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
@@ -3373,7 +3287,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="18.75" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>46</v>
       </c>
@@ -3423,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M4" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K4="","",IF(L4="","参照先未定義",_xlfn.XLOOKUP(L4,B:B,C:C,"エラー"))))</f>
@@ -3440,7 +3354,7 @@
       <c r="T4" s="9"/>
       <c r="U4" s="11"/>
     </row>
-    <row r="5" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="18.75" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>46</v>
       </c>
@@ -3461,7 +3375,7 @@
         <v>Vtuberプロフィール</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>67</v>
@@ -3490,7 +3404,7 @@
         <v>51</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="M5" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K5="","",IF(L5="","参照先未定義",_xlfn.XLOOKUP(L5,B:B,C:C,"エラー"))))</f>
@@ -3507,7 +3421,7 @@
       </c>
       <c r="U5" s="11"/>
     </row>
-    <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="18.75" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>46</v>
       </c>
@@ -3534,7 +3448,7 @@
         <v>73</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I6" s="11">
         <f>_xlfn.LET(
@@ -3570,7 +3484,7 @@
       </c>
       <c r="U6" s="11"/>
     </row>
-    <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="18.75" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>46</v>
       </c>
@@ -3620,7 +3534,7 @@
         <v>51</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="M7" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K7="","",IF(L7="","参照先未定義",_xlfn.XLOOKUP(L7,B:B,C:C,"エラー"))))</f>
@@ -3637,7 +3551,7 @@
       <c r="T7" s="9"/>
       <c r="U7" s="11"/>
     </row>
-    <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="18.75" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>46</v>
       </c>
@@ -3664,7 +3578,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I8" s="11">
         <f>_xlfn.LET(
@@ -3702,7 +3616,7 @@
       <c r="T8" s="9"/>
       <c r="U8" s="11"/>
     </row>
-    <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="18.75" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>46</v>
       </c>
@@ -3769,7 +3683,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="18.75" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
@@ -3796,7 +3710,7 @@
         <v>118</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I10" s="11">
         <f>_xlfn.LET(
@@ -3834,7 +3748,7 @@
       <c r="T10" s="9"/>
       <c r="U10" s="11"/>
     </row>
-    <row r="11" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="18.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>46</v>
       </c>
@@ -3901,7 +3815,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="18.75" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>46</v>
       </c>
@@ -3928,7 +3842,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I12" s="11">
         <f>_xlfn.LET(
@@ -3966,7 +3880,7 @@
       <c r="T12" s="9"/>
       <c r="U12" s="11"/>
     </row>
-    <row r="13" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="18.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>46</v>
       </c>
@@ -3979,7 +3893,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>67</v>
@@ -4011,7 +3925,7 @@
         <v>128</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="9"/>
@@ -4020,10 +3934,10 @@
         <v/>
       </c>
       <c r="N13" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P13" s="11" t="s">
         <v>52</v>
@@ -4034,7 +3948,7 @@
       <c r="T13" s="9"/>
       <c r="U13" s="11"/>
     </row>
-    <row r="14" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="18.75" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>46</v>
       </c>
@@ -4087,10 +4001,10 @@
         <v/>
       </c>
       <c r="N14" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -4101,7 +4015,7 @@
       </c>
       <c r="U14" s="11"/>
     </row>
-    <row r="15" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="18.75" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>46</v>
       </c>
@@ -4151,7 +4065,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="M15" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K15="","",IF(L15="","参照先未定義",_xlfn.XLOOKUP(L15,B:B,C:C,"エラー"))))</f>
@@ -4166,7 +4080,7 @@
       <c r="T15" s="9"/>
       <c r="U15" s="11"/>
     </row>
-    <row r="16" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="18.75" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>46</v>
       </c>
@@ -4227,7 +4141,7 @@
       <c r="T16" s="9"/>
       <c r="U16" s="11"/>
     </row>
-    <row r="17" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="18.75" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>46</v>
       </c>
@@ -4254,7 +4168,7 @@
         <v>111</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I17" s="11">
         <f>_xlfn.LET(
@@ -4292,7 +4206,7 @@
       <c r="T17" s="9"/>
       <c r="U17" s="11"/>
     </row>
-    <row r="18" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="18.75" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>46</v>
       </c>
@@ -4359,7 +4273,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="18.75" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>46</v>
       </c>
@@ -4386,7 +4300,7 @@
         <v>118</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I19" s="11">
         <f>_xlfn.LET(
@@ -4424,7 +4338,7 @@
       <c r="T19" s="9"/>
       <c r="U19" s="11"/>
     </row>
-    <row r="20" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="18.75" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>46</v>
       </c>
@@ -4491,7 +4405,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="18.75" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>46</v>
       </c>
@@ -4518,7 +4432,7 @@
         <v>122</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I21" s="11">
         <f>_xlfn.LET(
@@ -4556,7 +4470,7 @@
       <c r="T21" s="9"/>
       <c r="U21" s="11"/>
     </row>
-    <row r="22" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="18.75" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>46</v>
       </c>
@@ -4601,7 +4515,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="9"/>
@@ -4610,10 +4524,10 @@
         <v/>
       </c>
       <c r="N22" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P22" s="11" t="s">
         <v>52</v>
@@ -4624,7 +4538,7 @@
       <c r="T22" s="9"/>
       <c r="U22" s="11"/>
     </row>
-    <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="18.75" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>46</v>
       </c>
@@ -4677,10 +4591,10 @@
         <v/>
       </c>
       <c r="N23" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
@@ -4691,7 +4605,7 @@
       </c>
       <c r="U23" s="11"/>
     </row>
-    <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="18.75" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>46</v>
       </c>
@@ -4718,7 +4632,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I24" s="11">
         <f>_xlfn.LET(
@@ -4756,7 +4670,7 @@
       <c r="T24" s="9"/>
       <c r="U24" s="11"/>
     </row>
-    <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="18.75" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>46</v>
       </c>
@@ -4823,7 +4737,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="18.75" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>46</v>
       </c>
@@ -4850,7 +4764,7 @@
         <v>118</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I26" s="11">
         <f>_xlfn.LET(
@@ -4888,7 +4802,7 @@
       <c r="T26" s="9"/>
       <c r="U26" s="11"/>
     </row>
-    <row r="27" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="18.75" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>46</v>
       </c>
@@ -4955,7 +4869,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="18.75" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>46</v>
       </c>
@@ -4982,7 +4896,7 @@
         <v>122</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I28" s="11">
         <f>_xlfn.LET(
@@ -5020,7 +4934,7 @@
       <c r="T28" s="9"/>
       <c r="U28" s="11"/>
     </row>
-    <row r="29" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="18.75" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>46</v>
       </c>
@@ -5065,7 +4979,7 @@
         <v>128</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="9"/>
@@ -5074,10 +4988,10 @@
         <v/>
       </c>
       <c r="N29" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P29" s="11" t="s">
         <v>52</v>
@@ -5088,7 +5002,7 @@
       <c r="T29" s="9"/>
       <c r="U29" s="11"/>
     </row>
-    <row r="30" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="18.75" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>46</v>
       </c>
@@ -5141,10 +5055,10 @@
         <v/>
       </c>
       <c r="N30" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
@@ -5154,10 +5068,10 @@
         <v>51</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="18.75" customHeight="1">
       <c r="A31" s="9" t="s">
         <v>46</v>
       </c>
@@ -5184,7 +5098,7 @@
         <v>111</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I31" s="11">
         <f>_xlfn.LET(
@@ -5222,7 +5136,7 @@
       <c r="T31" s="9"/>
       <c r="U31" s="11"/>
     </row>
-    <row r="32" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="18.75" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>46</v>
       </c>
@@ -5289,7 +5203,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="18.75" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>46</v>
       </c>
@@ -5316,7 +5230,7 @@
         <v>118</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I33" s="11">
         <f>_xlfn.LET(
@@ -5354,7 +5268,7 @@
       <c r="T33" s="9"/>
       <c r="U33" s="11"/>
     </row>
-    <row r="34" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="18.75" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
@@ -5421,7 +5335,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="18.75" customHeight="1">
       <c r="A35" s="9" t="s">
         <v>46</v>
       </c>
@@ -5448,7 +5362,7 @@
         <v>122</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I35" s="11">
         <f>_xlfn.LET(
@@ -5486,7 +5400,7 @@
       <c r="T35" s="9"/>
       <c r="U35" s="11"/>
     </row>
-    <row r="36" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="18.75" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>46</v>
       </c>
@@ -5531,7 +5445,7 @@
         <v>128</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="9"/>
@@ -5540,10 +5454,10 @@
         <v/>
       </c>
       <c r="N36" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P36" s="11" t="s">
         <v>52</v>
@@ -5554,7 +5468,7 @@
       <c r="T36" s="9"/>
       <c r="U36" s="11"/>
     </row>
-    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="18.75" customHeight="1">
       <c r="A37" s="9" t="s">
         <v>46</v>
       </c>
@@ -5607,10 +5521,10 @@
         <v/>
       </c>
       <c r="N37" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
@@ -5618,10 +5532,10 @@
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
       <c r="U37" s="11" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="18.75" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>46</v>
       </c>
@@ -5648,7 +5562,7 @@
         <v>111</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I38" s="11">
         <f>_xlfn.LET(
@@ -5686,7 +5600,7 @@
       <c r="T38" s="9"/>
       <c r="U38" s="11"/>
     </row>
-    <row r="39" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="18.75" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>46</v>
       </c>
@@ -5753,7 +5667,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="18.75" customHeight="1">
       <c r="A40" s="9" t="s">
         <v>46</v>
       </c>
@@ -5780,7 +5694,7 @@
         <v>118</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I40" s="11">
         <f>_xlfn.LET(
@@ -5818,7 +5732,7 @@
       <c r="T40" s="9"/>
       <c r="U40" s="11"/>
     </row>
-    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="18.75" customHeight="1">
       <c r="A41" s="9" t="s">
         <v>46</v>
       </c>
@@ -5885,7 +5799,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="18.75" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>46</v>
       </c>
@@ -5912,7 +5826,7 @@
         <v>122</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I42" s="11">
         <f>_xlfn.LET(
@@ -5950,7 +5864,7 @@
       <c r="T42" s="9"/>
       <c r="U42" s="11"/>
     </row>
-    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="18.75" customHeight="1">
       <c r="A43" s="9" t="s">
         <v>46</v>
       </c>
@@ -5995,7 +5909,7 @@
         <v>128</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="9"/>
@@ -6004,10 +5918,10 @@
         <v/>
       </c>
       <c r="N43" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P43" s="11" t="s">
         <v>52</v>
@@ -6018,7 +5932,7 @@
       <c r="T43" s="9"/>
       <c r="U43" s="11"/>
     </row>
-    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="18.75" customHeight="1">
       <c r="A44" s="9" t="s">
         <v>46</v>
       </c>
@@ -6068,7 +5982,7 @@
         <v>51</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M44" s="11">
         <f>_xlfn.SINGLE(IF(K44="","",IF(L44="","参照先未定義",_xlfn.XLOOKUP(L44,B:B,C:C,"エラー"))))</f>
@@ -6085,7 +5999,7 @@
       <c r="T44" s="9"/>
       <c r="U44" s="11"/>
     </row>
-    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="18.75" customHeight="1">
       <c r="A45" s="9" t="s">
         <v>46</v>
       </c>
@@ -6135,7 +6049,7 @@
         <v>51</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="M45" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K45="","",IF(L45="","参照先未定義",_xlfn.XLOOKUP(L45,B:B,C:C,"エラー"))))</f>
@@ -6152,7 +6066,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="18.75" customHeight="1">
       <c r="A46" s="9" t="s">
         <v>46</v>
       </c>
@@ -6215,7 +6129,7 @@
       <c r="T46" s="9"/>
       <c r="U46" s="11"/>
     </row>
-    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="18.75" customHeight="1">
       <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
@@ -6278,7 +6192,7 @@
       <c r="T47" s="9"/>
       <c r="U47" s="11"/>
     </row>
-    <row r="48" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="18.75" customHeight="1">
       <c r="A48" s="9" t="s">
         <v>46</v>
       </c>
@@ -6305,7 +6219,7 @@
         <v>111</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I48" s="11">
         <f>_xlfn.LET(
@@ -6343,7 +6257,7 @@
       <c r="T48" s="9"/>
       <c r="U48" s="11"/>
     </row>
-    <row r="49" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="18.75" customHeight="1">
       <c r="A49" s="9" t="s">
         <v>46</v>
       </c>
@@ -6410,7 +6324,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="18.75" customHeight="1">
       <c r="A50" s="9" t="s">
         <v>46</v>
       </c>
@@ -6437,7 +6351,7 @@
         <v>118</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I50" s="11">
         <f>_xlfn.LET(
@@ -6475,7 +6389,7 @@
       <c r="T50" s="9"/>
       <c r="U50" s="11"/>
     </row>
-    <row r="51" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="18.75" customHeight="1">
       <c r="A51" s="9" t="s">
         <v>46</v>
       </c>
@@ -6542,7 +6456,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="18.75" customHeight="1">
       <c r="A52" s="9" t="s">
         <v>46</v>
       </c>
@@ -6569,7 +6483,7 @@
         <v>122</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I52" s="11">
         <f>_xlfn.LET(
@@ -6607,7 +6521,7 @@
       <c r="T52" s="9"/>
       <c r="U52" s="11"/>
     </row>
-    <row r="53" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="18.75" customHeight="1">
       <c r="A53" s="9" t="s">
         <v>46</v>
       </c>
@@ -6652,7 +6566,7 @@
         <v>128</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K53" s="11"/>
       <c r="L53" s="9"/>
@@ -6661,10 +6575,10 @@
         <v/>
       </c>
       <c r="N53" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P53" s="11" t="s">
         <v>52</v>
@@ -6675,7 +6589,7 @@
       <c r="T53" s="9"/>
       <c r="U53" s="11"/>
     </row>
-    <row r="54" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" ht="18.75" customHeight="1">
       <c r="A54" s="9" t="s">
         <v>46</v>
       </c>
@@ -6725,7 +6639,7 @@
         <v>51</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M54" s="11">
         <f>_xlfn.SINGLE(IF(K54="","",IF(L54="","参照先未定義",_xlfn.XLOOKUP(L54,B:B,C:C,"エラー"))))</f>
@@ -6742,7 +6656,7 @@
       <c r="T54" s="9"/>
       <c r="U54" s="11"/>
     </row>
-    <row r="55" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="18.75" customHeight="1">
       <c r="A55" s="9" t="s">
         <v>46</v>
       </c>
@@ -6792,7 +6706,7 @@
         <v>51</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M55" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K55="","",IF(L55="","参照先未定義",_xlfn.XLOOKUP(L55,B:B,C:C,"エラー"))))</f>
@@ -6809,7 +6723,7 @@
       <c r="T55" s="9"/>
       <c r="U55" s="11"/>
     </row>
-    <row r="56" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" ht="18.75" customHeight="1">
       <c r="A56" s="9" t="s">
         <v>46</v>
       </c>
@@ -6872,7 +6786,7 @@
       <c r="T56" s="9"/>
       <c r="U56" s="11"/>
     </row>
-    <row r="57" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="18.75" customHeight="1">
       <c r="A57" s="9" t="s">
         <v>46</v>
       </c>
@@ -6899,7 +6813,7 @@
         <v>152</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I57" s="11">
         <f>_xlfn.LET(
@@ -6935,7 +6849,7 @@
       <c r="T57" s="9"/>
       <c r="U57" s="11"/>
     </row>
-    <row r="58" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="18.75" customHeight="1">
       <c r="A58" s="9" t="s">
         <v>46</v>
       </c>
@@ -6962,7 +6876,7 @@
         <v>111</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I58" s="11">
         <f>_xlfn.LET(
@@ -7000,7 +6914,7 @@
       <c r="T58" s="9"/>
       <c r="U58" s="11"/>
     </row>
-    <row r="59" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="18.75" customHeight="1">
       <c r="A59" s="9" t="s">
         <v>46</v>
       </c>
@@ -7067,7 +6981,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="18.75" customHeight="1">
       <c r="A60" s="9" t="s">
         <v>46</v>
       </c>
@@ -7094,7 +7008,7 @@
         <v>118</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I60" s="11">
         <f>_xlfn.LET(
@@ -7132,7 +7046,7 @@
       <c r="T60" s="9"/>
       <c r="U60" s="11"/>
     </row>
-    <row r="61" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="18.75" customHeight="1">
       <c r="A61" s="9" t="s">
         <v>46</v>
       </c>
@@ -7199,7 +7113,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="18.75" customHeight="1">
       <c r="A62" s="9" t="s">
         <v>46</v>
       </c>
@@ -7226,7 +7140,7 @@
         <v>122</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I62" s="11">
         <f>_xlfn.LET(
@@ -7264,7 +7178,7 @@
       <c r="T62" s="9"/>
       <c r="U62" s="11"/>
     </row>
-    <row r="63" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="18.75" customHeight="1">
       <c r="A63" s="9" t="s">
         <v>46</v>
       </c>
@@ -7309,7 +7223,7 @@
         <v>128</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K63" s="11"/>
       <c r="L63" s="9"/>
@@ -7318,10 +7232,10 @@
         <v/>
       </c>
       <c r="N63" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P63" s="11" t="s">
         <v>52</v>
@@ -7332,7 +7246,7 @@
       <c r="T63" s="9"/>
       <c r="U63" s="11"/>
     </row>
-    <row r="64" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="18.75" customHeight="1">
       <c r="A64" s="9" t="s">
         <v>46</v>
       </c>
@@ -7382,7 +7296,7 @@
         <v>51</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M64" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K64="","",IF(L64="","参照先未定義",_xlfn.XLOOKUP(L64,B:B,C:C,"エラー"))))</f>
@@ -7399,7 +7313,7 @@
       <c r="T64" s="9"/>
       <c r="U64" s="11"/>
     </row>
-    <row r="65" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="18.75" customHeight="1">
       <c r="A65" s="9" t="s">
         <v>46</v>
       </c>
@@ -7449,7 +7363,7 @@
         <v>51</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M65" s="11">
         <f>_xlfn.SINGLE(IF(K65="","",IF(L65="","参照先未定義",_xlfn.XLOOKUP(L65,B:B,C:C,"エラー"))))</f>
@@ -7466,7 +7380,7 @@
       <c r="T65" s="9"/>
       <c r="U65" s="11"/>
     </row>
-    <row r="66" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="18.75" customHeight="1">
       <c r="A66" s="9" t="s">
         <v>46</v>
       </c>
@@ -7516,7 +7430,7 @@
         <v>51</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="M66" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K66="","",IF(L66="","参照先未定義",_xlfn.XLOOKUP(L66,B:B,C:C,"エラー"))))</f>
@@ -7533,7 +7447,7 @@
       <c r="T66" s="9"/>
       <c r="U66" s="11"/>
     </row>
-    <row r="67" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="18.75" customHeight="1">
       <c r="A67" s="9" t="s">
         <v>46</v>
       </c>
@@ -7596,7 +7510,7 @@
       <c r="T67" s="9"/>
       <c r="U67" s="11"/>
     </row>
-    <row r="68" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="18.75" customHeight="1">
       <c r="A68" s="9" t="s">
         <v>46</v>
       </c>
@@ -7659,7 +7573,7 @@
       <c r="T68" s="9"/>
       <c r="U68" s="11"/>
     </row>
-    <row r="69" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" ht="18.75" customHeight="1">
       <c r="A69" s="9" t="s">
         <v>46</v>
       </c>
@@ -7686,7 +7600,7 @@
         <v>161</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I69" s="11">
         <f>_xlfn.LET(
@@ -7724,7 +7638,7 @@
       <c r="T69" s="9"/>
       <c r="U69" s="11"/>
     </row>
-    <row r="70" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="18.75" customHeight="1">
       <c r="A70" s="9" t="s">
         <v>46</v>
       </c>
@@ -7789,7 +7703,7 @@
       <c r="T70" s="9"/>
       <c r="U70" s="11"/>
     </row>
-    <row r="71" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="18.75" customHeight="1">
       <c r="A71" s="9" t="s">
         <v>46</v>
       </c>
@@ -7816,7 +7730,7 @@
         <v>111</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I71" s="11">
         <f>_xlfn.LET(
@@ -7854,7 +7768,7 @@
       <c r="T71" s="9"/>
       <c r="U71" s="11"/>
     </row>
-    <row r="72" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="18.75" customHeight="1">
       <c r="A72" s="9" t="s">
         <v>46</v>
       </c>
@@ -7921,7 +7835,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" ht="18.75" customHeight="1">
       <c r="A73" s="9" t="s">
         <v>46</v>
       </c>
@@ -7948,7 +7862,7 @@
         <v>118</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I73" s="11">
         <f>_xlfn.LET(
@@ -7986,7 +7900,7 @@
       <c r="T73" s="9"/>
       <c r="U73" s="11"/>
     </row>
-    <row r="74" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="18.75" customHeight="1">
       <c r="A74" s="9" t="s">
         <v>46</v>
       </c>
@@ -8053,7 +7967,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="18.75" customHeight="1">
       <c r="A75" s="9" t="s">
         <v>46</v>
       </c>
@@ -8080,7 +7994,7 @@
         <v>122</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I75" s="11">
         <f>_xlfn.LET(
@@ -8118,7 +8032,7 @@
       <c r="T75" s="9"/>
       <c r="U75" s="11"/>
     </row>
-    <row r="76" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="18.75" customHeight="1">
       <c r="A76" s="9" t="s">
         <v>46</v>
       </c>
@@ -8163,7 +8077,7 @@
         <v>128</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K76" s="11"/>
       <c r="L76" s="9"/>
@@ -8172,10 +8086,10 @@
         <v/>
       </c>
       <c r="N76" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P76" s="11" t="s">
         <v>52</v>
@@ -8186,7 +8100,7 @@
       <c r="T76" s="9"/>
       <c r="U76" s="11"/>
     </row>
-    <row r="77" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="18.75" customHeight="1">
       <c r="A77" s="9" t="s">
         <v>46</v>
       </c>
@@ -8251,7 +8165,7 @@
       <c r="T77" s="9"/>
       <c r="U77" s="11"/>
     </row>
-    <row r="78" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="18.75" customHeight="1">
       <c r="A78" s="9" t="s">
         <v>46</v>
       </c>
@@ -8316,7 +8230,7 @@
       <c r="T78" s="9"/>
       <c r="U78" s="11"/>
     </row>
-    <row r="79" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="18.75" customHeight="1">
       <c r="A79" s="9" t="s">
         <v>46</v>
       </c>
@@ -8381,7 +8295,7 @@
       <c r="T79" s="9"/>
       <c r="U79" s="11"/>
     </row>
-    <row r="80" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="18.75" customHeight="1">
       <c r="A80" s="9" t="s">
         <v>46</v>
       </c>
@@ -8401,7 +8315,7 @@
         <f t="array" aca="1" ref="E80" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>問い合わせ</v>
       </c>
-      <c r="F80" s="21" t="s">
+      <c r="F80" s="11" t="s">
         <v>173</v>
       </c>
       <c r="G80" s="11" t="s">
@@ -8431,7 +8345,7 @@
         <v>51</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="M80" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K80="","",IF(L80="","参照先未定義",_xlfn.XLOOKUP(L80,B:B,C:C,"エラー"))))</f>
@@ -8446,7 +8360,7 @@
       <c r="T80" s="9"/>
       <c r="U80" s="11"/>
     </row>
-    <row r="81" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" ht="18.75" customHeight="1">
       <c r="A81" s="9" t="s">
         <v>46</v>
       </c>
@@ -8466,7 +8380,7 @@
         <f t="array" aca="1" ref="E81" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>問い合わせ</v>
       </c>
-      <c r="F81" s="21" t="s">
+      <c r="F81" s="11" t="s">
         <v>175</v>
       </c>
       <c r="G81" s="11" t="s">
@@ -8496,7 +8410,7 @@
         <v>51</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="M81" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K81="","",IF(L81="","参照先未定義",_xlfn.XLOOKUP(L81,B:B,C:C,"エラー"))))</f>
@@ -8511,7 +8425,7 @@
       <c r="T81" s="9"/>
       <c r="U81" s="11"/>
     </row>
-    <row r="82" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="18.75" customHeight="1">
       <c r="A82" s="9" t="s">
         <v>46</v>
       </c>
@@ -8538,7 +8452,7 @@
         <v>111</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I82" s="11">
         <f>_xlfn.LET(
@@ -8576,7 +8490,7 @@
       <c r="T82" s="9"/>
       <c r="U82" s="11"/>
     </row>
-    <row r="83" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" ht="18.75" customHeight="1">
       <c r="A83" s="9" t="s">
         <v>46</v>
       </c>
@@ -8643,7 +8557,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" ht="18.75" customHeight="1">
       <c r="A84" s="9" t="s">
         <v>46</v>
       </c>
@@ -8670,7 +8584,7 @@
         <v>118</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I84" s="11">
         <f>_xlfn.LET(
@@ -8708,7 +8622,7 @@
       <c r="T84" s="9"/>
       <c r="U84" s="11"/>
     </row>
-    <row r="85" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="18.75" customHeight="1">
       <c r="A85" s="9" t="s">
         <v>46</v>
       </c>
@@ -8775,7 +8689,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" ht="18.75" customHeight="1">
       <c r="A86" s="9" t="s">
         <v>46</v>
       </c>
@@ -8802,7 +8716,7 @@
         <v>122</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I86" s="11">
         <f>_xlfn.LET(
@@ -8840,7 +8754,7 @@
       <c r="T86" s="9"/>
       <c r="U86" s="11"/>
     </row>
-    <row r="87" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" ht="18.75" customHeight="1">
       <c r="A87" s="9" t="s">
         <v>46</v>
       </c>
@@ -8885,7 +8799,7 @@
         <v>128</v>
       </c>
       <c r="J87" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K87" s="11"/>
       <c r="L87" s="9"/>
@@ -8894,10 +8808,10 @@
         <v/>
       </c>
       <c r="N87" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P87" s="11" t="s">
         <v>52</v>
@@ -8908,7 +8822,7 @@
       <c r="T87" s="9"/>
       <c r="U87" s="11"/>
     </row>
-    <row r="88" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="18.75" customHeight="1">
       <c r="A88" s="9" t="s">
         <v>46</v>
       </c>
@@ -8961,10 +8875,10 @@
         <v/>
       </c>
       <c r="N88" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P88" s="11"/>
       <c r="Q88" s="11"/>
@@ -8973,7 +8887,7 @@
       <c r="T88" s="9"/>
       <c r="U88" s="11"/>
     </row>
-    <row r="89" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" ht="18.75" customHeight="1">
       <c r="A89" s="9" t="s">
         <v>46</v>
       </c>
@@ -9033,10 +8947,10 @@
       <c r="S89" s="9"/>
       <c r="T89" s="9"/>
       <c r="U89" s="11" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="18.75" customHeight="1">
       <c r="A90" s="9" t="s">
         <v>46</v>
       </c>
@@ -9063,7 +8977,7 @@
         <v>111</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I90" s="11">
         <f>_xlfn.LET(
@@ -9101,7 +9015,7 @@
       <c r="T90" s="9"/>
       <c r="U90" s="11"/>
     </row>
-    <row r="91" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="18.75" customHeight="1">
       <c r="A91" s="9" t="s">
         <v>46</v>
       </c>
@@ -9168,7 +9082,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="18.75" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>46</v>
       </c>
@@ -9195,7 +9109,7 @@
         <v>118</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I92" s="11">
         <f>_xlfn.LET(
@@ -9233,7 +9147,7 @@
       <c r="T92" s="9"/>
       <c r="U92" s="11"/>
     </row>
-    <row r="93" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="18.75" customHeight="1">
       <c r="A93" s="9" t="s">
         <v>46</v>
       </c>
@@ -9300,7 +9214,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" ht="18.75" customHeight="1">
       <c r="A94" s="9" t="s">
         <v>46</v>
       </c>
@@ -9327,7 +9241,7 @@
         <v>122</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I94" s="11">
         <f>_xlfn.LET(
@@ -9365,7 +9279,7 @@
       <c r="T94" s="9"/>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="18.75" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>46</v>
       </c>
@@ -9410,7 +9324,7 @@
         <v>128</v>
       </c>
       <c r="J95" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K95" s="11"/>
       <c r="L95" s="9"/>
@@ -9419,10 +9333,10 @@
         <v/>
       </c>
       <c r="N95" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P95" s="11" t="s">
         <v>52</v>
@@ -9433,7 +9347,7 @@
       <c r="T95" s="9"/>
       <c r="U95" s="11"/>
     </row>
-    <row r="96" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" ht="18.75" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>46</v>
       </c>
@@ -9486,10 +9400,10 @@
         <v/>
       </c>
       <c r="N96" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P96" s="11"/>
       <c r="Q96" s="11"/>
@@ -9498,7 +9412,7 @@
       <c r="T96" s="9"/>
       <c r="U96" s="11"/>
     </row>
-    <row r="97" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" ht="18.75" customHeight="1">
       <c r="A97" s="9" t="s">
         <v>46</v>
       </c>
@@ -9558,10 +9472,10 @@
       <c r="S97" s="9"/>
       <c r="T97" s="9"/>
       <c r="U97" s="11" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="18.75" customHeight="1">
       <c r="A98" s="9" t="s">
         <v>46</v>
       </c>
@@ -9588,7 +9502,7 @@
         <v>111</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I98" s="11">
         <f>_xlfn.LET(
@@ -9626,7 +9540,7 @@
       <c r="T98" s="9"/>
       <c r="U98" s="11"/>
     </row>
-    <row r="99" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" ht="18.75" customHeight="1">
       <c r="A99" s="9" t="s">
         <v>46</v>
       </c>
@@ -9693,7 +9607,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" ht="18.75" customHeight="1">
       <c r="A100" s="9" t="s">
         <v>46</v>
       </c>
@@ -9720,7 +9634,7 @@
         <v>118</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I100" s="11">
         <f>_xlfn.LET(
@@ -9758,7 +9672,7 @@
       <c r="T100" s="9"/>
       <c r="U100" s="11"/>
     </row>
-    <row r="101" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" ht="18.75" customHeight="1">
       <c r="A101" s="9" t="s">
         <v>46</v>
       </c>
@@ -9825,7 +9739,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" ht="18.75" customHeight="1">
       <c r="A102" s="9" t="s">
         <v>46</v>
       </c>
@@ -9852,7 +9766,7 @@
         <v>122</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I102" s="11">
         <f>_xlfn.LET(
@@ -9890,7 +9804,7 @@
       <c r="T102" s="9"/>
       <c r="U102" s="11"/>
     </row>
-    <row r="103" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" ht="18.75" customHeight="1">
       <c r="A103" s="9" t="s">
         <v>46</v>
       </c>
@@ -9935,7 +9849,7 @@
         <v>128</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K103" s="11"/>
       <c r="L103" s="9"/>
@@ -9944,10 +9858,10 @@
         <v/>
       </c>
       <c r="N103" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P103" s="11" t="s">
         <v>52</v>
@@ -9958,7 +9872,7 @@
       <c r="T103" s="9"/>
       <c r="U103" s="11"/>
     </row>
-    <row r="104" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" ht="18.75" customHeight="1">
       <c r="A104" s="9" t="s">
         <v>46</v>
       </c>
@@ -10011,10 +9925,10 @@
         <v/>
       </c>
       <c r="N104" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O104" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P104" s="11"/>
       <c r="Q104" s="11"/>
@@ -10022,10 +9936,10 @@
       <c r="S104" s="9"/>
       <c r="T104" s="9"/>
       <c r="U104" s="11" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="18.75" customHeight="1">
       <c r="A105" s="9" t="s">
         <v>46</v>
       </c>
@@ -10088,7 +10002,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" ht="18.75" customHeight="1">
       <c r="A106" s="9" t="s">
         <v>46</v>
       </c>
@@ -10115,7 +10029,7 @@
         <v>193</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I106" s="11">
         <f>_xlfn.LET(
@@ -10153,7 +10067,7 @@
       <c r="T106" s="9"/>
       <c r="U106" s="11"/>
     </row>
-    <row r="107" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" ht="18.75" customHeight="1">
       <c r="A107" s="9" t="s">
         <v>46</v>
       </c>
@@ -10180,7 +10094,7 @@
         <v>111</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I107" s="11">
         <f>_xlfn.LET(
@@ -10218,7 +10132,7 @@
       <c r="T107" s="9"/>
       <c r="U107" s="11"/>
     </row>
-    <row r="108" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="18.75" customHeight="1">
       <c r="A108" s="9" t="s">
         <v>46</v>
       </c>
@@ -10285,7 +10199,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" ht="18.75" customHeight="1">
       <c r="A109" s="9" t="s">
         <v>46</v>
       </c>
@@ -10312,7 +10226,7 @@
         <v>118</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I109" s="11">
         <f>_xlfn.LET(
@@ -10350,7 +10264,7 @@
       <c r="T109" s="9"/>
       <c r="U109" s="11"/>
     </row>
-    <row r="110" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" ht="18.75" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>46</v>
       </c>
@@ -10417,7 +10331,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" ht="18.75" customHeight="1">
       <c r="A111" s="9" t="s">
         <v>46</v>
       </c>
@@ -10444,7 +10358,7 @@
         <v>122</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I111" s="11">
         <f>_xlfn.LET(
@@ -10482,7 +10396,7 @@
       <c r="T111" s="9"/>
       <c r="U111" s="11"/>
     </row>
-    <row r="112" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" ht="18.75" customHeight="1">
       <c r="A112" s="9" t="s">
         <v>46</v>
       </c>
@@ -10527,7 +10441,7 @@
         <v>128</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K112" s="11"/>
       <c r="L112" s="9"/>
@@ -10536,10 +10450,10 @@
         <v/>
       </c>
       <c r="N112" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O112" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P112" s="11" t="s">
         <v>52</v>
@@ -10550,7 +10464,7 @@
       <c r="T112" s="9"/>
       <c r="U112" s="11"/>
     </row>
-    <row r="113" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" ht="18.75" customHeight="1">
       <c r="A113" s="9" t="s">
         <v>46</v>
       </c>
@@ -10570,7 +10484,7 @@
         <f t="array" aca="1" ref="E113" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>画面文言</v>
       </c>
-      <c r="F113" s="21" t="s">
+      <c r="F113" s="11" t="s">
         <v>187</v>
       </c>
       <c r="G113" s="11" t="s">
@@ -10600,7 +10514,7 @@
         <v>51</v>
       </c>
       <c r="L113" s="9" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="M113" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K113="","",IF(L113="","参照先未定義",_xlfn.XLOOKUP(L113,B:B,C:C,"エラー"))))</f>
@@ -10615,7 +10529,7 @@
       <c r="T113" s="9"/>
       <c r="U113" s="11"/>
     </row>
-    <row r="114" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" ht="18.75" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>46</v>
       </c>
@@ -10665,7 +10579,7 @@
         <v>51</v>
       </c>
       <c r="L114" s="9" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="M114" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K114="","",IF(L114="","参照先未定義",_xlfn.XLOOKUP(L114,B:B,C:C,"エラー"))))</f>
@@ -10682,7 +10596,7 @@
       <c r="T114" s="9"/>
       <c r="U114" s="11"/>
     </row>
-    <row r="115" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" ht="18.75" customHeight="1">
       <c r="A115" s="9" t="s">
         <v>46</v>
       </c>
@@ -10738,14 +10652,14 @@
       <c r="O115" s="11"/>
       <c r="P115" s="11"/>
       <c r="Q115" s="11" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="R115" s="9"/>
       <c r="S115" s="9"/>
       <c r="T115" s="9"/>
       <c r="U115" s="11"/>
     </row>
-    <row r="116" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" ht="18.75" customHeight="1">
       <c r="A116" s="9"/>
       <c r="B116" s="9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10764,13 +10678,13 @@
         <v>画面文言</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="G116" s="11" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="I116" s="11" t="str">
         <f>_xlfn.LET(
@@ -10799,16 +10713,16 @@
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
       <c r="Q116" s="11" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
       <c r="T116" s="9"/>
       <c r="U116" s="11" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="117" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" ht="18.75" customHeight="1">
       <c r="A117" s="9" t="s">
         <v>46</v>
       </c>
@@ -10835,7 +10749,7 @@
         <v>111</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I117" s="11">
         <f>_xlfn.LET(
@@ -10873,7 +10787,7 @@
       <c r="T117" s="9"/>
       <c r="U117" s="11"/>
     </row>
-    <row r="118" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" ht="18.75" customHeight="1">
       <c r="A118" s="9" t="s">
         <v>46</v>
       </c>
@@ -10940,7 +10854,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" ht="18.75" customHeight="1">
       <c r="A119" s="9" t="s">
         <v>46</v>
       </c>
@@ -10967,7 +10881,7 @@
         <v>118</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I119" s="11">
         <f>_xlfn.LET(
@@ -11005,7 +10919,7 @@
       <c r="T119" s="9"/>
       <c r="U119" s="11"/>
     </row>
-    <row r="120" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" ht="18.75" customHeight="1">
       <c r="A120" s="9" t="s">
         <v>46</v>
       </c>
@@ -11072,7 +10986,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" ht="18.75" customHeight="1">
       <c r="A121" s="9" t="s">
         <v>46</v>
       </c>
@@ -11099,7 +11013,7 @@
         <v>122</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I121" s="11">
         <f>_xlfn.LET(
@@ -11137,7 +11051,7 @@
       <c r="T121" s="9"/>
       <c r="U121" s="11"/>
     </row>
-    <row r="122" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" ht="18.75" customHeight="1">
       <c r="A122" s="9" t="s">
         <v>46</v>
       </c>
@@ -11182,7 +11096,7 @@
         <v>128</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K122" s="11"/>
       <c r="L122" s="9"/>
@@ -11191,10 +11105,10 @@
         <v/>
       </c>
       <c r="N122" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O122" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P122" s="11" t="s">
         <v>52</v>
@@ -11205,7 +11119,7 @@
       <c r="T122" s="9"/>
       <c r="U122" s="11"/>
     </row>
-    <row r="123" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" ht="18.75" customHeight="1">
       <c r="A123" s="9" t="s">
         <v>46</v>
       </c>
@@ -11225,14 +11139,14 @@
         <f t="array" aca="1" ref="E123" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>サポートするSNS</v>
       </c>
-      <c r="F123" s="21" t="s">
+      <c r="F123" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>204</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="I123" s="11">
         <f>_xlfn.LET(
@@ -11255,17 +11169,17 @@
         <v>51</v>
       </c>
       <c r="L123" s="9" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="M123" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K123="","",IF(L123="","参照先未定義",_xlfn.XLOOKUP(L123,B:B,C:C,"エラー"))))</f>
         <v>102</v>
       </c>
       <c r="N123" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O123" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P123" s="11"/>
       <c r="Q123" s="11"/>
@@ -11274,7 +11188,7 @@
       <c r="T123" s="9"/>
       <c r="U123" s="11"/>
     </row>
-    <row r="124" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" ht="18.75" customHeight="1">
       <c r="A124" s="9" t="s">
         <v>46</v>
       </c>
@@ -11324,7 +11238,7 @@
         <v>51</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="M124" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K124="","",IF(L124="","参照先未定義",_xlfn.XLOOKUP(L124,B:B,C:C,"エラー"))))</f>
@@ -11345,7 +11259,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" ht="18.75" customHeight="1">
       <c r="A125" s="9" t="s">
         <v>46</v>
       </c>
@@ -11372,7 +11286,7 @@
         <v>209</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I125" s="11">
         <f>_xlfn.LET(
@@ -11410,7 +11324,7 @@
       <c r="T125" s="9"/>
       <c r="U125" s="11"/>
     </row>
-    <row r="126" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" ht="18.75" customHeight="1">
       <c r="A126" s="9" t="s">
         <v>46</v>
       </c>
@@ -11437,7 +11351,7 @@
         <v>211</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I126" s="11">
         <f>_xlfn.LET(
@@ -11475,7 +11389,7 @@
       <c r="T126" s="9"/>
       <c r="U126" s="11"/>
     </row>
-    <row r="127" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" ht="18.75" customHeight="1">
       <c r="A127" s="9" t="s">
         <v>46</v>
       </c>
@@ -11502,7 +11416,7 @@
         <v>111</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I127" s="11">
         <f>_xlfn.LET(
@@ -11540,7 +11454,7 @@
       <c r="T127" s="9"/>
       <c r="U127" s="11"/>
     </row>
-    <row r="128" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" ht="18.75" customHeight="1">
       <c r="A128" s="9" t="s">
         <v>46</v>
       </c>
@@ -11607,7 +11521,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" ht="18.75" customHeight="1">
       <c r="A129" s="9" t="s">
         <v>46</v>
       </c>
@@ -11634,7 +11548,7 @@
         <v>118</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I129" s="11">
         <f>_xlfn.LET(
@@ -11672,7 +11586,7 @@
       <c r="T129" s="9"/>
       <c r="U129" s="11"/>
     </row>
-    <row r="130" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" ht="18.75" customHeight="1">
       <c r="A130" s="9" t="s">
         <v>46</v>
       </c>
@@ -11739,7 +11653,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" ht="18.75" customHeight="1">
       <c r="A131" s="9" t="s">
         <v>46</v>
       </c>
@@ -11766,7 +11680,7 @@
         <v>122</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I131" s="11">
         <f>_xlfn.LET(
@@ -11804,7 +11718,7 @@
       <c r="T131" s="9"/>
       <c r="U131" s="11"/>
     </row>
-    <row r="132" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" ht="18.75" customHeight="1">
       <c r="A132" s="9" t="s">
         <v>46</v>
       </c>
@@ -11849,7 +11763,7 @@
         <v>128</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K132" s="11"/>
       <c r="L132" s="9"/>
@@ -11858,10 +11772,10 @@
         <v/>
       </c>
       <c r="N132" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P132" s="11" t="s">
         <v>52</v>
@@ -11872,7 +11786,7 @@
       <c r="T132" s="9"/>
       <c r="U132" s="11"/>
     </row>
-    <row r="133" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" ht="18.75" customHeight="1">
       <c r="A133" s="9" t="s">
         <v>46</v>
       </c>
@@ -11922,7 +11836,7 @@
         <v>51</v>
       </c>
       <c r="L133" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M133" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K133="","",IF(L133="","参照先未定義",_xlfn.XLOOKUP(L133,B:B,C:C,"エラー"))))</f>
@@ -11937,7 +11851,7 @@
       <c r="T133" s="9"/>
       <c r="U133" s="11"/>
     </row>
-    <row r="134" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" ht="18.75" customHeight="1">
       <c r="A134" s="9" t="s">
         <v>46</v>
       </c>
@@ -11987,7 +11901,7 @@
         <v>51</v>
       </c>
       <c r="L134" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M134" s="11">
         <f>_xlfn.SINGLE(IF(K134="","",IF(L134="","参照先未定義",_xlfn.XLOOKUP(L134,B:B,C:C,"エラー"))))</f>
@@ -12004,7 +11918,7 @@
       <c r="T134" s="9"/>
       <c r="U134" s="11"/>
     </row>
-    <row r="135" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" ht="18.75" customHeight="1">
       <c r="A135" s="9" t="s">
         <v>46</v>
       </c>
@@ -12024,7 +11938,7 @@
         <f t="array" aca="1" ref="E135" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>プロフィール通報</v>
       </c>
-      <c r="F135" s="21" t="s">
+      <c r="F135" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G135" s="11" t="s">
@@ -12054,7 +11968,7 @@
         <v>51</v>
       </c>
       <c r="L135" s="9" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="M135" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K135="","",IF(L135="","参照先未定義",_xlfn.XLOOKUP(L135,B:B,C:C,"エラー"))))</f>
@@ -12073,7 +11987,7 @@
       <c r="T135" s="9"/>
       <c r="U135" s="11"/>
     </row>
-    <row r="136" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" ht="18.75" customHeight="1">
       <c r="A136" s="9" t="s">
         <v>46</v>
       </c>
@@ -12138,7 +12052,7 @@
       <c r="T136" s="9"/>
       <c r="U136" s="11"/>
     </row>
-    <row r="137" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" ht="18.75" customHeight="1">
       <c r="A137" s="9" t="s">
         <v>46</v>
       </c>
@@ -12165,7 +12079,7 @@
         <v>219</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I137" s="11">
         <f>_xlfn.LET(
@@ -12203,7 +12117,7 @@
       <c r="T137" s="9"/>
       <c r="U137" s="11"/>
     </row>
-    <row r="138" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" ht="18.75" customHeight="1">
       <c r="A138" s="9" t="s">
         <v>46</v>
       </c>
@@ -12230,7 +12144,7 @@
         <v>111</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I138" s="11">
         <f>_xlfn.LET(
@@ -12268,7 +12182,7 @@
       <c r="T138" s="9"/>
       <c r="U138" s="11"/>
     </row>
-    <row r="139" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" ht="18.75" customHeight="1">
       <c r="A139" s="9" t="s">
         <v>46</v>
       </c>
@@ -12335,7 +12249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" ht="18.75" customHeight="1">
       <c r="A140" s="9" t="s">
         <v>46</v>
       </c>
@@ -12362,7 +12276,7 @@
         <v>118</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I140" s="11">
         <f>_xlfn.LET(
@@ -12400,7 +12314,7 @@
       <c r="T140" s="9"/>
       <c r="U140" s="11"/>
     </row>
-    <row r="141" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" ht="18.75" customHeight="1">
       <c r="A141" s="9" t="s">
         <v>46</v>
       </c>
@@ -12467,7 +12381,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" ht="18.75" customHeight="1">
       <c r="A142" s="9" t="s">
         <v>46</v>
       </c>
@@ -12494,7 +12408,7 @@
         <v>122</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I142" s="11">
         <f>_xlfn.LET(
@@ -12532,7 +12446,7 @@
       <c r="T142" s="9"/>
       <c r="U142" s="11"/>
     </row>
-    <row r="143" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" ht="18.75" customHeight="1">
       <c r="A143" s="9" t="s">
         <v>46</v>
       </c>
@@ -12577,7 +12491,7 @@
         <v>128</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K143" s="11"/>
       <c r="L143" s="9"/>
@@ -12586,10 +12500,10 @@
         <v/>
       </c>
       <c r="N143" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O143" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P143" s="11" t="s">
         <v>52</v>
@@ -12600,7 +12514,7 @@
       <c r="T143" s="9"/>
       <c r="U143" s="11"/>
     </row>
-    <row r="144" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" ht="18.75" customHeight="1">
       <c r="A144" s="9" t="s">
         <v>46</v>
       </c>
@@ -12620,7 +12534,7 @@
         <f t="array" aca="1" ref="E144" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>通報理由</v>
       </c>
-      <c r="F144" s="21" t="s">
+      <c r="F144" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G144" s="11" t="s">
@@ -12653,10 +12567,10 @@
         <v/>
       </c>
       <c r="N144" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O144" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P144" s="11"/>
       <c r="Q144" s="11"/>
@@ -12664,10 +12578,10 @@
       <c r="S144" s="9"/>
       <c r="T144" s="9"/>
       <c r="U144" s="11" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" ht="18.75" customHeight="1">
       <c r="A145" s="9" t="s">
         <v>46</v>
       </c>
@@ -12694,7 +12608,7 @@
         <v>111</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I145" s="11">
         <f>_xlfn.LET(
@@ -12732,7 +12646,7 @@
       <c r="T145" s="9"/>
       <c r="U145" s="11"/>
     </row>
-    <row r="146" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" ht="18.75" customHeight="1">
       <c r="A146" s="9" t="s">
         <v>46</v>
       </c>
@@ -12799,7 +12713,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" ht="18.75" customHeight="1">
       <c r="A147" s="9" t="s">
         <v>46</v>
       </c>
@@ -12826,7 +12740,7 @@
         <v>118</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I147" s="11">
         <f>_xlfn.LET(
@@ -12864,7 +12778,7 @@
       <c r="T147" s="9"/>
       <c r="U147" s="11"/>
     </row>
-    <row r="148" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" ht="18.75" customHeight="1">
       <c r="A148" s="9" t="s">
         <v>46</v>
       </c>
@@ -12931,7 +12845,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" ht="18.75" customHeight="1">
       <c r="A149" s="9" t="s">
         <v>46</v>
       </c>
@@ -12958,7 +12872,7 @@
         <v>122</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I149" s="11">
         <f>_xlfn.LET(
@@ -12996,7 +12910,7 @@
       <c r="T149" s="9"/>
       <c r="U149" s="11"/>
     </row>
-    <row r="150" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" ht="18.75" customHeight="1">
       <c r="A150" s="9" t="s">
         <v>46</v>
       </c>
@@ -13009,7 +12923,7 @@
         <v>149</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="E150" s="11" t="s">
         <v>222</v>
@@ -13041,7 +12955,7 @@
         <v>128</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K150" s="11"/>
       <c r="L150" s="9"/>
@@ -13050,10 +12964,10 @@
         <v/>
       </c>
       <c r="N150" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O150" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P150" s="11" t="s">
         <v>52</v>
@@ -13064,7 +12978,7 @@
       <c r="T150" s="9"/>
       <c r="U150" s="11"/>
     </row>
-    <row r="151" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" ht="18.75" customHeight="1">
       <c r="A151" s="9" t="s">
         <v>46</v>
       </c>
@@ -13117,10 +13031,10 @@
         <v/>
       </c>
       <c r="N151" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O151" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P151" s="11" t="s">
         <v>56</v>
@@ -13131,7 +13045,7 @@
       <c r="T151" s="9"/>
       <c r="U151" s="11"/>
     </row>
-    <row r="152" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" ht="18.75" customHeight="1">
       <c r="A152" s="9" t="s">
         <v>46</v>
       </c>
@@ -13192,7 +13106,7 @@
       <c r="T152" s="9"/>
       <c r="U152" s="11"/>
     </row>
-    <row r="153" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" ht="18.75" customHeight="1">
       <c r="A153" s="9" t="s">
         <v>46</v>
       </c>
@@ -13212,7 +13126,7 @@
         <f t="array" aca="1" ref="E153" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>ユーザー</v>
       </c>
-      <c r="F153" s="21" t="s">
+      <c r="F153" s="11" t="s">
         <v>223</v>
       </c>
       <c r="G153" s="11" t="s">
@@ -13242,7 +13156,7 @@
         <v>51</v>
       </c>
       <c r="L153" s="9" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="M153" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K153="","",IF(L153="","参照先未定義",_xlfn.XLOOKUP(L153,B:B,C:C,"エラー"))))</f>
@@ -13257,7 +13171,7 @@
       <c r="T153" s="9"/>
       <c r="U153" s="11"/>
     </row>
-    <row r="154" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" ht="18.75" customHeight="1">
       <c r="A154" s="9" t="s">
         <v>46</v>
       </c>
@@ -13284,7 +13198,7 @@
         <v>226</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I154" s="11">
         <f>_xlfn.LET(
@@ -13324,7 +13238,7 @@
       <c r="T154" s="9"/>
       <c r="U154" s="11"/>
     </row>
-    <row r="155" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" ht="18.75" customHeight="1">
       <c r="A155" s="9" t="s">
         <v>46</v>
       </c>
@@ -13374,7 +13288,7 @@
         <v>51</v>
       </c>
       <c r="L155" s="9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="M155" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K155="","",IF(L155="","参照先未定義",_xlfn.XLOOKUP(L155,B:B,C:C,"エラー"))))</f>
@@ -13389,7 +13303,7 @@
       <c r="T155" s="9"/>
       <c r="U155" s="11"/>
     </row>
-    <row r="156" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" ht="18.75" customHeight="1">
       <c r="A156" s="9" t="s">
         <v>46</v>
       </c>
@@ -13416,7 +13330,7 @@
         <v>231</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I156" s="11">
         <f>_xlfn.LET(
@@ -13454,7 +13368,7 @@
       <c r="T156" s="9"/>
       <c r="U156" s="11"/>
     </row>
-    <row r="157" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" ht="18.75" customHeight="1">
       <c r="A157" s="9" t="s">
         <v>46</v>
       </c>
@@ -13504,7 +13418,7 @@
         <v>51</v>
       </c>
       <c r="L157" s="9" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="M157" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K157="","",IF(L157="","参照先未定義",_xlfn.XLOOKUP(L157,B:B,C:C,"エラー"))))</f>
@@ -13515,7 +13429,7 @@
       </c>
       <c r="O157" s="11"/>
       <c r="P157" s="11" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="Q157" s="11"/>
       <c r="R157" s="9"/>
@@ -13523,7 +13437,7 @@
       <c r="T157" s="9"/>
       <c r="U157" s="11"/>
     </row>
-    <row r="158" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" ht="18.75" customHeight="1">
       <c r="A158" s="9" t="s">
         <v>46</v>
       </c>
@@ -13573,7 +13487,7 @@
         <v>51</v>
       </c>
       <c r="L158" s="9" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="M158" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K158="","",IF(L158="","参照先未定義",_xlfn.XLOOKUP(L158,B:B,C:C,"エラー"))))</f>
@@ -13584,7 +13498,7 @@
       </c>
       <c r="O158" s="11"/>
       <c r="P158" s="11" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="Q158" s="11"/>
       <c r="R158" s="9"/>
@@ -13592,7 +13506,7 @@
       <c r="T158" s="9"/>
       <c r="U158" s="11"/>
     </row>
-    <row r="159" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" ht="18.75" customHeight="1">
       <c r="A159" s="9" t="s">
         <v>46</v>
       </c>
@@ -13619,7 +13533,7 @@
         <v>111</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I159" s="11">
         <f>_xlfn.LET(
@@ -13657,7 +13571,7 @@
       <c r="T159" s="9"/>
       <c r="U159" s="11"/>
     </row>
-    <row r="160" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" ht="18.75" customHeight="1">
       <c r="A160" s="9" t="s">
         <v>46</v>
       </c>
@@ -13724,7 +13638,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" ht="18.75" customHeight="1">
       <c r="A161" s="9" t="s">
         <v>46</v>
       </c>
@@ -13751,7 +13665,7 @@
         <v>118</v>
       </c>
       <c r="H161" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I161" s="11">
         <f>_xlfn.LET(
@@ -13789,7 +13703,7 @@
       <c r="T161" s="9"/>
       <c r="U161" s="11"/>
     </row>
-    <row r="162" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" ht="18.75" customHeight="1">
       <c r="A162" s="9" t="s">
         <v>46</v>
       </c>
@@ -13856,7 +13770,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" ht="18.75" customHeight="1">
       <c r="A163" s="9" t="s">
         <v>46</v>
       </c>
@@ -13883,7 +13797,7 @@
         <v>122</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I163" s="11">
         <f>_xlfn.LET(
@@ -13921,7 +13835,7 @@
       <c r="T163" s="9"/>
       <c r="U163" s="11"/>
     </row>
-    <row r="164" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" ht="18.75" customHeight="1">
       <c r="A164" s="9" t="s">
         <v>46</v>
       </c>
@@ -13966,7 +13880,7 @@
         <v>128</v>
       </c>
       <c r="J164" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K164" s="11"/>
       <c r="L164" s="9"/>
@@ -13975,10 +13889,10 @@
         <v/>
       </c>
       <c r="N164" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O164" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P164" s="11" t="s">
         <v>52</v>
@@ -13989,7 +13903,7 @@
       <c r="T164" s="9"/>
       <c r="U164" s="11"/>
     </row>
-    <row r="165" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" ht="18.75" customHeight="1">
       <c r="A165" s="9" t="s">
         <v>46</v>
       </c>
@@ -14042,10 +13956,10 @@
         <v/>
       </c>
       <c r="N165" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O165" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P165" s="11"/>
       <c r="Q165" s="11"/>
@@ -14053,10 +13967,10 @@
       <c r="S165" s="9"/>
       <c r="T165" s="9"/>
       <c r="U165" s="11" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="166" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" ht="18.75" customHeight="1">
       <c r="A166" s="9" t="s">
         <v>46</v>
       </c>
@@ -14083,7 +13997,7 @@
         <v>111</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I166" s="11">
         <f>_xlfn.LET(
@@ -14121,7 +14035,7 @@
       <c r="T166" s="9"/>
       <c r="U166" s="11"/>
     </row>
-    <row r="167" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" ht="18.75" customHeight="1">
       <c r="A167" s="9" t="s">
         <v>46</v>
       </c>
@@ -14188,7 +14102,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" ht="18.75" customHeight="1">
       <c r="A168" s="9" t="s">
         <v>46</v>
       </c>
@@ -14215,7 +14129,7 @@
         <v>118</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I168" s="11">
         <f>_xlfn.LET(
@@ -14253,7 +14167,7 @@
       <c r="T168" s="9"/>
       <c r="U168" s="11"/>
     </row>
-    <row r="169" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" ht="18.75" customHeight="1">
       <c r="A169" s="9" t="s">
         <v>46</v>
       </c>
@@ -14320,7 +14234,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" ht="18.75" customHeight="1">
       <c r="A170" s="9" t="s">
         <v>46</v>
       </c>
@@ -14347,7 +14261,7 @@
         <v>122</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I170" s="11">
         <f>_xlfn.LET(
@@ -14385,7 +14299,7 @@
       <c r="T170" s="9"/>
       <c r="U170" s="11"/>
     </row>
-    <row r="171" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" ht="18.75" customHeight="1">
       <c r="A171" s="9" t="s">
         <v>46</v>
       </c>
@@ -14430,7 +14344,7 @@
         <v>128</v>
       </c>
       <c r="J171" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K171" s="11"/>
       <c r="L171" s="9"/>
@@ -14439,10 +14353,10 @@
         <v/>
       </c>
       <c r="N171" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O171" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P171" s="11" t="s">
         <v>52</v>
@@ -14453,7 +14367,7 @@
       <c r="T171" s="9"/>
       <c r="U171" s="11"/>
     </row>
-    <row r="172" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" ht="18.75" customHeight="1">
       <c r="A172" s="9" t="s">
         <v>46</v>
       </c>
@@ -14506,10 +14420,10 @@
         <v/>
       </c>
       <c r="N172" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O172" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P172" s="11"/>
       <c r="Q172" s="11"/>
@@ -14517,10 +14431,10 @@
       <c r="S172" s="9"/>
       <c r="T172" s="9"/>
       <c r="U172" s="11" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="173" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" ht="18.75" customHeight="1">
       <c r="A173" s="9" t="s">
         <v>46</v>
       </c>
@@ -14547,7 +14461,7 @@
         <v>111</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I173" s="11">
         <f>_xlfn.LET(
@@ -14585,7 +14499,7 @@
       <c r="T173" s="9"/>
       <c r="U173" s="11"/>
     </row>
-    <row r="174" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" ht="18.75" customHeight="1">
       <c r="A174" s="9" t="s">
         <v>46</v>
       </c>
@@ -14652,7 +14566,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" ht="18.75" customHeight="1">
       <c r="A175" s="9" t="s">
         <v>46</v>
       </c>
@@ -14679,7 +14593,7 @@
         <v>118</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I175" s="11">
         <f>_xlfn.LET(
@@ -14717,7 +14631,7 @@
       <c r="T175" s="9"/>
       <c r="U175" s="11"/>
     </row>
-    <row r="176" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" ht="18.75" customHeight="1">
       <c r="A176" s="9" t="s">
         <v>46</v>
       </c>
@@ -14784,7 +14698,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" ht="18.75" customHeight="1">
       <c r="A177" s="9" t="s">
         <v>46</v>
       </c>
@@ -14811,7 +14725,7 @@
         <v>122</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I177" s="11">
         <f>_xlfn.LET(
@@ -14849,7 +14763,7 @@
       <c r="T177" s="9"/>
       <c r="U177" s="11"/>
     </row>
-    <row r="178" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" ht="18.75" customHeight="1">
       <c r="A178" s="9" t="s">
         <v>46</v>
       </c>
@@ -14862,7 +14776,7 @@
         <v>177</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="E178" s="11" t="s">
         <v>239</v>
@@ -14894,7 +14808,7 @@
         <v>128</v>
       </c>
       <c r="J178" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K178" s="11"/>
       <c r="L178" s="9"/>
@@ -14903,10 +14817,10 @@
         <v/>
       </c>
       <c r="N178" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O178" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P178" s="11" t="s">
         <v>52</v>
@@ -14917,7 +14831,7 @@
       <c r="T178" s="9"/>
       <c r="U178" s="11"/>
     </row>
-    <row r="179" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" ht="18.75" customHeight="1">
       <c r="A179" s="9" t="s">
         <v>46</v>
       </c>
@@ -14970,10 +14884,10 @@
         <v/>
       </c>
       <c r="N179" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O179" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P179" s="11"/>
       <c r="Q179" s="11"/>
@@ -14982,7 +14896,7 @@
       <c r="T179" s="9"/>
       <c r="U179" s="11"/>
     </row>
-    <row r="180" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" ht="18.75" customHeight="1">
       <c r="A180" s="9" t="s">
         <v>46</v>
       </c>
@@ -15032,7 +14946,7 @@
         <v>51</v>
       </c>
       <c r="L180" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M180" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K180="","",IF(L180="","参照先未定義",_xlfn.XLOOKUP(L180,B:B,C:C,"エラー"))))</f>
@@ -15049,7 +14963,7 @@
       <c r="T180" s="9"/>
       <c r="U180" s="11"/>
     </row>
-    <row r="181" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" ht="18.75" customHeight="1">
       <c r="A181" s="9" t="s">
         <v>46</v>
       </c>
@@ -15112,7 +15026,7 @@
       <c r="T181" s="9"/>
       <c r="U181" s="11"/>
     </row>
-    <row r="182" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" ht="18.75" customHeight="1">
       <c r="A182" s="9" t="s">
         <v>46</v>
       </c>
@@ -15177,12 +15091,12 @@
       <c r="T182" s="9"/>
       <c r="U182" s="11"/>
     </row>
-    <row r="183" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" ht="18.75" customHeight="1">
       <c r="A183" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B183" s="9" t="str">
-        <f t="shared" ref="B183:B246" ca="1" si="5">D183&amp;"."&amp;F183</f>
+        <f t="shared" ref="B183:B237" ca="1" si="5">D183&amp;"."&amp;F183</f>
         <v>images_contents.cdn_url</v>
       </c>
       <c r="C183" s="10">
@@ -15240,7 +15154,7 @@
       <c r="T183" s="9"/>
       <c r="U183" s="11"/>
     </row>
-    <row r="184" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" ht="18.75" customHeight="1">
       <c r="A184" s="9" t="s">
         <v>46</v>
       </c>
@@ -15303,7 +15217,7 @@
       <c r="T184" s="9"/>
       <c r="U184" s="11"/>
     </row>
-    <row r="185" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" ht="18.75" customHeight="1">
       <c r="A185" s="9" t="s">
         <v>46</v>
       </c>
@@ -15364,7 +15278,7 @@
       <c r="T185" s="9"/>
       <c r="U185" s="11"/>
     </row>
-    <row r="186" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" ht="18.75" customHeight="1">
       <c r="A186" s="9" t="s">
         <v>46</v>
       </c>
@@ -15425,7 +15339,7 @@
       <c r="T186" s="9"/>
       <c r="U186" s="11"/>
     </row>
-    <row r="187" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" ht="18.75" customHeight="1">
       <c r="A187" s="9" t="s">
         <v>46</v>
       </c>
@@ -15486,7 +15400,7 @@
       <c r="T187" s="9"/>
       <c r="U187" s="11"/>
     </row>
-    <row r="188" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" ht="18.75" customHeight="1">
       <c r="A188" s="9" t="s">
         <v>46</v>
       </c>
@@ -15547,7 +15461,7 @@
       <c r="T188" s="9"/>
       <c r="U188" s="11"/>
     </row>
-    <row r="189" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" ht="18.75" customHeight="1">
       <c r="A189" s="9" t="s">
         <v>46</v>
       </c>
@@ -15574,7 +15488,7 @@
         <v>111</v>
       </c>
       <c r="H189" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I189" s="11">
         <f>_xlfn.LET(
@@ -15612,7 +15526,7 @@
       <c r="T189" s="9"/>
       <c r="U189" s="11"/>
     </row>
-    <row r="190" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" ht="18.75" customHeight="1">
       <c r="A190" s="9" t="s">
         <v>46</v>
       </c>
@@ -15679,7 +15593,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" ht="18.75" customHeight="1">
       <c r="A191" s="9" t="s">
         <v>46</v>
       </c>
@@ -15706,7 +15620,7 @@
         <v>118</v>
       </c>
       <c r="H191" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I191" s="11">
         <f>_xlfn.LET(
@@ -15744,7 +15658,7 @@
       <c r="T191" s="9"/>
       <c r="U191" s="11"/>
     </row>
-    <row r="192" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" ht="18.75" customHeight="1">
       <c r="A192" s="9" t="s">
         <v>46</v>
       </c>
@@ -15811,7 +15725,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" ht="18.75" customHeight="1">
       <c r="A193" s="9" t="s">
         <v>46</v>
       </c>
@@ -15838,7 +15752,7 @@
         <v>122</v>
       </c>
       <c r="H193" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I193" s="11">
         <f>_xlfn.LET(
@@ -15876,7 +15790,7 @@
       <c r="T193" s="9"/>
       <c r="U193" s="11"/>
     </row>
-    <row r="194" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" ht="18.75" customHeight="1">
       <c r="A194" s="9" t="s">
         <v>46</v>
       </c>
@@ -15889,7 +15803,7 @@
         <v>193</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E194" s="11" t="s">
         <v>261</v>
@@ -15921,7 +15835,7 @@
         <v>128</v>
       </c>
       <c r="J194" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K194" s="11"/>
       <c r="L194" s="9"/>
@@ -15930,10 +15844,10 @@
         <v/>
       </c>
       <c r="N194" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O194" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P194" s="11" t="s">
         <v>52</v>
@@ -15944,7 +15858,7 @@
       <c r="T194" s="9"/>
       <c r="U194" s="11"/>
     </row>
-    <row r="195" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" ht="18.75" customHeight="1">
       <c r="A195" s="9" t="s">
         <v>46</v>
       </c>
@@ -15997,10 +15911,10 @@
         <v/>
       </c>
       <c r="N195" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O195" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P195" s="11"/>
       <c r="Q195" s="11"/>
@@ -16009,7 +15923,7 @@
       <c r="T195" s="9"/>
       <c r="U195" s="11"/>
     </row>
-    <row r="196" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" ht="18.75" customHeight="1">
       <c r="A196" s="9" t="s">
         <v>46</v>
       </c>
@@ -16072,7 +15986,7 @@
       <c r="T196" s="9"/>
       <c r="U196" s="11"/>
     </row>
-    <row r="197" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" ht="18.75" customHeight="1">
       <c r="A197" s="9" t="s">
         <v>46</v>
       </c>
@@ -16137,7 +16051,7 @@
       <c r="T197" s="9"/>
       <c r="U197" s="11"/>
     </row>
-    <row r="198" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" ht="18.75" customHeight="1">
       <c r="A198" s="9" t="s">
         <v>46</v>
       </c>
@@ -16200,7 +16114,7 @@
       <c r="T198" s="9"/>
       <c r="U198" s="11"/>
     </row>
-    <row r="199" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" ht="18.75" customHeight="1">
       <c r="A199" s="9" t="s">
         <v>46</v>
       </c>
@@ -16209,7 +16123,7 @@
         <v>images_system.content_type</v>
       </c>
       <c r="C199" s="10">
-        <f t="shared" ref="C199:C254" si="6">ROW()-1</f>
+        <f t="shared" ref="C199:C245" si="6">ROW()-1</f>
         <v>198</v>
       </c>
       <c r="D199" s="11" t="str" cm="1">
@@ -16263,7 +16177,7 @@
       <c r="T199" s="9"/>
       <c r="U199" s="11"/>
     </row>
-    <row r="200" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" ht="18.75" customHeight="1">
       <c r="A200" s="9" t="s">
         <v>46</v>
       </c>
@@ -16324,7 +16238,7 @@
       <c r="T200" s="9"/>
       <c r="U200" s="11"/>
     </row>
-    <row r="201" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" ht="18.75" customHeight="1">
       <c r="A201" s="9" t="s">
         <v>46</v>
       </c>
@@ -16385,7 +16299,7 @@
       <c r="T201" s="9"/>
       <c r="U201" s="11"/>
     </row>
-    <row r="202" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" ht="18.75" customHeight="1">
       <c r="A202" s="9" t="s">
         <v>46</v>
       </c>
@@ -16446,7 +16360,7 @@
       <c r="T202" s="9"/>
       <c r="U202" s="11"/>
     </row>
-    <row r="203" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" ht="18.75" customHeight="1">
       <c r="A203" s="9" t="s">
         <v>46</v>
       </c>
@@ -16507,7 +16421,7 @@
       <c r="T203" s="9"/>
       <c r="U203" s="11"/>
     </row>
-    <row r="204" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" ht="18.75" customHeight="1">
       <c r="A204" s="9" t="s">
         <v>46</v>
       </c>
@@ -16534,7 +16448,7 @@
         <v>111</v>
       </c>
       <c r="H204" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I204" s="11">
         <f>_xlfn.LET(
@@ -16572,7 +16486,7 @@
       <c r="T204" s="9"/>
       <c r="U204" s="11"/>
     </row>
-    <row r="205" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" ht="18.75" customHeight="1">
       <c r="A205" s="9" t="s">
         <v>46</v>
       </c>
@@ -16639,7 +16553,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" ht="18.75" customHeight="1">
       <c r="A206" s="9" t="s">
         <v>46</v>
       </c>
@@ -16666,7 +16580,7 @@
         <v>118</v>
       </c>
       <c r="H206" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I206" s="11">
         <f>_xlfn.LET(
@@ -16704,7 +16618,7 @@
       <c r="T206" s="9"/>
       <c r="U206" s="11"/>
     </row>
-    <row r="207" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" ht="18.75" customHeight="1">
       <c r="A207" s="9" t="s">
         <v>46</v>
       </c>
@@ -16771,7 +16685,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" ht="18.75" customHeight="1">
       <c r="A208" s="9" t="s">
         <v>46</v>
       </c>
@@ -16798,7 +16712,7 @@
         <v>122</v>
       </c>
       <c r="H208" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I208" s="11">
         <f>_xlfn.LET(
@@ -16836,7 +16750,7 @@
       <c r="T208" s="9"/>
       <c r="U208" s="11"/>
     </row>
-    <row r="209" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" ht="18.75" customHeight="1">
       <c r="A209" s="9" t="s">
         <v>46</v>
       </c>
@@ -16881,7 +16795,7 @@
         <v>128</v>
       </c>
       <c r="J209" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K209" s="11"/>
       <c r="L209" s="9"/>
@@ -16890,10 +16804,10 @@
         <v/>
       </c>
       <c r="N209" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O209" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P209" s="11" t="s">
         <v>52</v>
@@ -16904,7 +16818,7 @@
       <c r="T209" s="9"/>
       <c r="U209" s="11"/>
     </row>
-    <row r="210" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" ht="18.75" customHeight="1">
       <c r="A210" s="9" t="s">
         <v>46</v>
       </c>
@@ -16957,10 +16871,10 @@
         <v/>
       </c>
       <c r="N210" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O210" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P210" s="11"/>
       <c r="Q210" s="11" t="s">
@@ -16971,7 +16885,7 @@
       <c r="T210" s="9"/>
       <c r="U210" s="11"/>
     </row>
-    <row r="211" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" ht="18.75" customHeight="1">
       <c r="A211" s="9" t="s">
         <v>46</v>
       </c>
@@ -16998,7 +16912,7 @@
         <v>111</v>
       </c>
       <c r="H211" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I211" s="11">
         <f>_xlfn.LET(
@@ -17036,7 +16950,7 @@
       <c r="T211" s="9"/>
       <c r="U211" s="11"/>
     </row>
-    <row r="212" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" ht="18.75" customHeight="1">
       <c r="A212" s="9" t="s">
         <v>46</v>
       </c>
@@ -17103,7 +17017,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" ht="18.75" customHeight="1">
       <c r="A213" s="9" t="s">
         <v>46</v>
       </c>
@@ -17130,7 +17044,7 @@
         <v>118</v>
       </c>
       <c r="H213" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I213" s="11">
         <f>_xlfn.LET(
@@ -17168,7 +17082,7 @@
       <c r="T213" s="9"/>
       <c r="U213" s="11"/>
     </row>
-    <row r="214" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" ht="18.75" customHeight="1">
       <c r="A214" s="9" t="s">
         <v>46</v>
       </c>
@@ -17235,7 +17149,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" ht="18.75" customHeight="1">
       <c r="A215" s="9" t="s">
         <v>46</v>
       </c>
@@ -17262,7 +17176,7 @@
         <v>122</v>
       </c>
       <c r="H215" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I215" s="11">
         <f>_xlfn.LET(
@@ -17300,7 +17214,7 @@
       <c r="T215" s="9"/>
       <c r="U215" s="11"/>
     </row>
-    <row r="216" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" ht="18.75" customHeight="1">
       <c r="A216" s="9" t="s">
         <v>46</v>
       </c>
@@ -17313,7 +17227,7 @@
         <v>215</v>
       </c>
       <c r="D216" s="11" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="E216" s="11" t="s">
         <v>104</v>
@@ -17345,7 +17259,7 @@
         <v>128</v>
       </c>
       <c r="J216" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K216" s="11"/>
       <c r="L216" s="9"/>
@@ -17354,10 +17268,10 @@
         <v/>
       </c>
       <c r="N216" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O216" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P216" s="11" t="s">
         <v>52</v>
@@ -17368,7 +17282,7 @@
       <c r="T216" s="9"/>
       <c r="U216" s="11"/>
     </row>
-    <row r="217" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" ht="18.75" customHeight="1">
       <c r="A217" s="9" t="s">
         <v>46</v>
       </c>
@@ -17381,14 +17295,14 @@
         <v>216</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="E217" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E217" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
         <v>いいね</v>
       </c>
       <c r="F217" s="11" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="G217" s="11" t="s">
         <v>264</v>
@@ -17414,10 +17328,10 @@
       </c>
       <c r="J217" s="11"/>
       <c r="K217" s="11" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="L217" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M217" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K217="","",IF(L217="","参照先未定義",_xlfn.XLOOKUP(L217,B:B,C:C,"エラー"))))</f>
@@ -17427,18 +17341,18 @@
         <v>51</v>
       </c>
       <c r="O217" s="11" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="P217" s="11"/>
       <c r="Q217" s="11" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="R217" s="9"/>
       <c r="S217" s="9"/>
       <c r="T217" s="9"/>
       <c r="U217" s="11"/>
     </row>
-    <row r="218" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" ht="18.75" customHeight="1">
       <c r="A218" s="9" t="s">
         <v>46</v>
       </c>
@@ -17459,7 +17373,7 @@
         <v>いいね</v>
       </c>
       <c r="F218" s="11" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="G218" s="11" t="s">
         <v>265</v>
@@ -17485,10 +17399,10 @@
       </c>
       <c r="J218" s="11"/>
       <c r="K218" s="11" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="L218" s="9" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="M218" s="11">
         <f ca="1">_xlfn.SINGLE(IF(K218="","",IF(L218="","参照先未定義",_xlfn.XLOOKUP(L218,B:B,C:C,"エラー"))))</f>
@@ -17498,18 +17412,18 @@
         <v>51</v>
       </c>
       <c r="O218" s="11" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="P218" s="11"/>
       <c r="Q218" s="11" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="R218" s="9"/>
       <c r="S218" s="9"/>
       <c r="T218" s="9"/>
       <c r="U218" s="11"/>
     </row>
-    <row r="219" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" ht="18.75" customHeight="1">
       <c r="A219" s="9" t="s">
         <v>46</v>
       </c>
@@ -17530,13 +17444,13 @@
         <v>いいね</v>
       </c>
       <c r="F219" s="11" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="G219" s="11" t="s">
         <v>266</v>
       </c>
       <c r="H219" s="11" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="I219" s="11" t="str">
         <f>_xlfn.LET(
@@ -17565,18 +17479,18 @@
         <v>51</v>
       </c>
       <c r="O219" s="11" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="P219" s="11"/>
       <c r="Q219" s="11" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="R219" s="9"/>
       <c r="S219" s="9"/>
       <c r="T219" s="9"/>
       <c r="U219" s="11"/>
     </row>
-    <row r="220" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" ht="18.75" customHeight="1">
       <c r="A220" s="9" t="s">
         <v>46</v>
       </c>
@@ -17597,13 +17511,13 @@
         <v>いいね</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="G220" s="11" t="s">
         <v>267</v>
       </c>
       <c r="H220" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I220" s="11">
         <f>_xlfn.LET(
@@ -17639,7 +17553,7 @@
       <c r="T220" s="9"/>
       <c r="U220" s="11"/>
     </row>
-    <row r="221" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" ht="18.75" customHeight="1">
       <c r="A221" s="9" t="s">
         <v>46</v>
       </c>
@@ -17666,7 +17580,7 @@
         <v>111</v>
       </c>
       <c r="H221" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I221" s="11">
         <f>_xlfn.LET(
@@ -17704,7 +17618,7 @@
       <c r="T221" s="9"/>
       <c r="U221" s="11"/>
     </row>
-    <row r="222" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" ht="18.75" customHeight="1">
       <c r="A222" s="9" t="s">
         <v>46</v>
       </c>
@@ -17771,7 +17685,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" ht="18.75" customHeight="1">
       <c r="A223" s="9" t="s">
         <v>46</v>
       </c>
@@ -17798,7 +17712,7 @@
         <v>118</v>
       </c>
       <c r="H223" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I223" s="11">
         <f>_xlfn.LET(
@@ -17836,7 +17750,7 @@
       <c r="T223" s="9"/>
       <c r="U223" s="11"/>
     </row>
-    <row r="224" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" ht="18.75" customHeight="1">
       <c r="A224" s="9" t="s">
         <v>46</v>
       </c>
@@ -17903,7 +17817,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" ht="18.75" customHeight="1">
       <c r="A225" s="9" t="s">
         <v>46</v>
       </c>
@@ -17930,7 +17844,7 @@
         <v>122</v>
       </c>
       <c r="H225" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I225" s="11">
         <f>_xlfn.LET(
@@ -17968,7 +17882,7 @@
       <c r="T225" s="9"/>
       <c r="U225" s="11"/>
     </row>
-    <row r="226" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" ht="18.75" customHeight="1">
       <c r="A226" s="9" t="s">
         <v>46</v>
       </c>
@@ -18013,7 +17927,7 @@
         <v>128</v>
       </c>
       <c r="J226" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K226" s="11"/>
       <c r="L226" s="9"/>
@@ -18022,10 +17936,10 @@
         <v/>
       </c>
       <c r="N226" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O226" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P226" s="11" t="s">
         <v>52</v>
@@ -18036,7 +17950,7 @@
       <c r="T226" s="9"/>
       <c r="U226" s="11"/>
     </row>
-    <row r="227" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" ht="18.75" customHeight="1">
       <c r="A227" s="9" t="s">
         <v>46</v>
       </c>
@@ -18089,10 +18003,10 @@
         <v/>
       </c>
       <c r="N227" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="O227" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="P227" s="11"/>
       <c r="Q227" s="11"/>
@@ -18101,7 +18015,7 @@
       <c r="T227" s="9"/>
       <c r="U227" s="11"/>
     </row>
-    <row r="228" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" ht="18.75" customHeight="1">
       <c r="A228" s="9" t="s">
         <v>46</v>
       </c>
@@ -18151,7 +18065,7 @@
         <v>51</v>
       </c>
       <c r="L228" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M228" s="11">
         <f>_xlfn.SINGLE(IF(K228="","",IF(L228="","参照先未定義",_xlfn.XLOOKUP(L228,B:B,C:C,"エラー"))))</f>
@@ -18168,7 +18082,7 @@
       <c r="T228" s="9"/>
       <c r="U228" s="11"/>
     </row>
-    <row r="229" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" ht="18.75" customHeight="1">
       <c r="A229" s="9" t="s">
         <v>46</v>
       </c>
@@ -18231,7 +18145,7 @@
       <c r="T229" s="9"/>
       <c r="U229" s="11"/>
     </row>
-    <row r="230" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" ht="18.75" customHeight="1">
       <c r="A230" s="9" t="s">
         <v>46</v>
       </c>
@@ -18258,7 +18172,7 @@
         <v>111</v>
       </c>
       <c r="H230" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I230" s="11">
         <f>_xlfn.LET(
@@ -18296,7 +18210,7 @@
       <c r="T230" s="9"/>
       <c r="U230" s="11"/>
     </row>
-    <row r="231" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" ht="18.75" customHeight="1">
       <c r="A231" s="9" t="s">
         <v>46</v>
       </c>
@@ -18363,7 +18277,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" ht="18.75" customHeight="1">
       <c r="A232" s="9" t="s">
         <v>46</v>
       </c>
@@ -18390,7 +18304,7 @@
         <v>118</v>
       </c>
       <c r="H232" s="11" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="I232" s="11">
         <f>_xlfn.LET(
@@ -18428,7 +18342,7 @@
       <c r="T232" s="9"/>
       <c r="U232" s="11"/>
     </row>
-    <row r="233" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" ht="18.75" customHeight="1">
       <c r="A233" s="9" t="s">
         <v>46</v>
       </c>
@@ -18495,7 +18409,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" ht="18.75" customHeight="1">
       <c r="A234" s="9" t="s">
         <v>46</v>
       </c>
@@ -18522,7 +18436,7 @@
         <v>122</v>
       </c>
       <c r="H234" s="11" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="I234" s="11">
         <f>_xlfn.LET(
@@ -18560,27 +18474,27 @@
       <c r="T234" s="9"/>
       <c r="U234" s="11"/>
     </row>
-    <row r="235" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" ht="18.75" customHeight="1">
       <c r="A235" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B235" s="9" t="str">
         <f t="shared" si="5"/>
-        <v>relation.relation_uuid</v>
+        <v>vtuber_profiles_lang.vtuber_profiles_lang_uuid</v>
       </c>
       <c r="C235" s="10">
         <f t="shared" si="6"/>
         <v>234</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>273</v>
+        <v>452</v>
       </c>
       <c r="E235" s="11" t="s">
-        <v>274</v>
+        <v>451</v>
       </c>
       <c r="F235" s="11" t="str">
         <f>D235&amp;"_uuid"</f>
-        <v>relation_uuid</v>
+        <v>vtuber_profiles_lang_uuid</v>
       </c>
       <c r="G235" s="11" t="s">
         <v>50</v>
@@ -18605,7 +18519,7 @@
         <v>128</v>
       </c>
       <c r="J235" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="K235" s="11"/>
       <c r="L235" s="9"/>
@@ -18614,10 +18528,10 @@
         <v/>
       </c>
       <c r="N235" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="O235" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P235" s="11" t="s">
         <v>52</v>
@@ -18628,13 +18542,13 @@
       <c r="T235" s="9"/>
       <c r="U235" s="11"/>
     </row>
-    <row r="236" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" ht="18.75" customHeight="1">
       <c r="A236" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B236" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>relation.node_from</v>
+        <v>vtuber_profiles_lang.vtuber_profiles_id</v>
       </c>
       <c r="C236" s="10">
         <f t="shared" si="6"/>
@@ -18642,17 +18556,17 @@
       </c>
       <c r="D236" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D236" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E236" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E236" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>275</v>
+        <v>54</v>
       </c>
       <c r="H236" s="11" t="s">
         <v>49</v>
@@ -18675,10 +18589,10 @@
       </c>
       <c r="J236" s="11"/>
       <c r="K236" s="11" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
       <c r="L236" s="9" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="M236" s="11">
         <f>_xlfn.SINGLE(IF(K236="","",IF(L236="","参照先未定義",_xlfn.XLOOKUP(L236,B:B,C:C,"エラー"))))</f>
@@ -18688,24 +18602,24 @@
         <v>51</v>
       </c>
       <c r="O236" s="11" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="P236" s="11"/>
       <c r="Q236" s="11" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="R236" s="9"/>
       <c r="S236" s="9"/>
       <c r="T236" s="9"/>
       <c r="U236" s="11"/>
     </row>
-    <row r="237" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" ht="18.75" customHeight="1">
       <c r="A237" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B237" s="9" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>relation.node_to</v>
+        <v>vtuber_profiles_lang.lang</v>
       </c>
       <c r="C237" s="10">
         <f t="shared" si="6"/>
@@ -18713,17 +18627,17 @@
       </c>
       <c r="D237" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D237" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E237" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E237" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>277</v>
+        <v>457</v>
       </c>
       <c r="H237" s="11" t="s">
         <v>49</v>
@@ -18746,37 +18660,37 @@
       </c>
       <c r="J237" s="11"/>
       <c r="K237" s="11" t="s">
-        <v>51</v>
+        <v>456</v>
       </c>
       <c r="L237" s="9" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="M237" s="11">
-        <f>_xlfn.SINGLE(IF(K237="","",IF(L237="","参照先未定義",_xlfn.XLOOKUP(L237,B:B,C:C,"エラー"))))</f>
-        <v>1</v>
+        <f ca="1">IF(K237="","",IF(L237="","参照先未定義",_xlfn.XLOOKUP(L237,B:B,C:C,"エラー")))</f>
+        <v>102</v>
       </c>
       <c r="N237" s="11" t="s">
         <v>51</v>
       </c>
       <c r="O237" s="11" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="P237" s="11"/>
       <c r="Q237" s="11" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="R237" s="9"/>
       <c r="S237" s="9"/>
       <c r="T237" s="9"/>
       <c r="U237" s="11"/>
     </row>
-    <row r="238" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" ht="18.75" customHeight="1">
       <c r="A238" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B238" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.node_name</v>
+        <f t="shared" ref="B238:B266" ca="1" si="7">D238&amp;"."&amp;F238</f>
+        <v>vtuber_profiles_lang.name</v>
       </c>
       <c r="C238" s="10">
         <f t="shared" si="6"/>
@@ -18784,20 +18698,20 @@
       </c>
       <c r="D238" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D238" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E238" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E238" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>279</v>
+        <v>63</v>
       </c>
       <c r="H238" s="11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I238" s="11">
         <f>_xlfn.LET(
@@ -18813,13 +18727,13 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="J238" s="11"/>
       <c r="K238" s="11"/>
       <c r="L238" s="9"/>
       <c r="M238" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K238="","",IF(L238="","参照先未定義",_xlfn.XLOOKUP(L238,B:B,C:C,"エラー"))))</f>
+        <f>IF(K238="","",IF(L238="","参照先未定義",_xlfn.XLOOKUP(L238,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
       <c r="N238" s="11" t="s">
@@ -18828,18 +18742,22 @@
       <c r="O238" s="11"/>
       <c r="P238" s="11"/>
       <c r="Q238" s="11"/>
-      <c r="R238" s="9"/>
+      <c r="R238" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="S238" s="9"/>
-      <c r="T238" s="9"/>
+      <c r="T238" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U238" s="11"/>
     </row>
-    <row r="239" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" ht="18.75" customHeight="1">
       <c r="A239" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B239" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.create_datetime</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.nickname</v>
       </c>
       <c r="C239" s="10">
         <f t="shared" si="6"/>
@@ -18847,20 +18765,20 @@
       </c>
       <c r="D239" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D239" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E239" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E239" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="H239" s="11" t="s">
-        <v>502</v>
+        <v>64</v>
       </c>
       <c r="I239" s="11">
         <f>_xlfn.LET(
@@ -18876,35 +18794,33 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>1024</v>
       </c>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
       <c r="L239" s="9"/>
       <c r="M239" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K239="","",IF(L239="","参照先未定義",_xlfn.XLOOKUP(L239,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N239" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(K239="","",IF(L239="","参照先未定義",_xlfn.XLOOKUP(L239,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N239" s="11"/>
       <c r="O239" s="11"/>
-      <c r="P239" s="11" t="s">
-        <v>112</v>
-      </c>
+      <c r="P239" s="11"/>
       <c r="Q239" s="11"/>
       <c r="R239" s="9"/>
       <c r="S239" s="9"/>
-      <c r="T239" s="9"/>
+      <c r="T239" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U239" s="11"/>
     </row>
-    <row r="240" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" ht="18.75" customHeight="1">
       <c r="A240" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B240" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.create_user</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.birthday</v>
       </c>
       <c r="C240" s="10">
         <f t="shared" si="6"/>
@@ -18912,17 +18828,17 @@
       </c>
       <c r="D240" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D240" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E240" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E240" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="H240" s="11" t="s">
         <v>71</v>
@@ -18947,31 +18863,27 @@
       <c r="K240" s="11"/>
       <c r="L240" s="9"/>
       <c r="M240" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K240="","",IF(L240="","参照先未定義",_xlfn.XLOOKUP(L240,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N240" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(K240="","",IF(L240="","参照先未定義",_xlfn.XLOOKUP(L240,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N240" s="11"/>
       <c r="O240" s="11"/>
-      <c r="P240" s="11" t="s">
-        <v>115</v>
-      </c>
+      <c r="P240" s="11"/>
       <c r="Q240" s="11"/>
       <c r="R240" s="9"/>
       <c r="S240" s="9"/>
-      <c r="T240" s="9"/>
-      <c r="U240" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="241" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T240" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U240" s="11"/>
+    </row>
+    <row r="241" spans="1:21" ht="18.75" customHeight="1">
       <c r="A241" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B241" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.update_datetime</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.blood_type</v>
       </c>
       <c r="C241" s="10">
         <f t="shared" si="6"/>
@@ -18979,20 +18891,20 @@
       </c>
       <c r="D241" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D241" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E241" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E241" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="H241" s="11" t="s">
-        <v>502</v>
+        <v>77</v>
       </c>
       <c r="I241" s="11">
         <f>_xlfn.LET(
@@ -19008,35 +18920,33 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J241" s="11"/>
       <c r="K241" s="11"/>
       <c r="L241" s="9"/>
       <c r="M241" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K241="","",IF(L241="","参照先未定義",_xlfn.XLOOKUP(L241,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N241" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(K241="","",IF(L241="","参照先未定義",_xlfn.XLOOKUP(L241,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N241" s="11"/>
       <c r="O241" s="11"/>
-      <c r="P241" s="11" t="s">
-        <v>112</v>
-      </c>
+      <c r="P241" s="11"/>
       <c r="Q241" s="11"/>
       <c r="R241" s="9"/>
       <c r="S241" s="9"/>
-      <c r="T241" s="9"/>
+      <c r="T241" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U241" s="11"/>
     </row>
-    <row r="242" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" ht="18.75" customHeight="1">
       <c r="A242" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B242" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.update_user</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.height</v>
       </c>
       <c r="C242" s="10">
         <f t="shared" si="6"/>
@@ -19044,20 +18954,20 @@
       </c>
       <c r="D242" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D242" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E242" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E242" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I242" s="11">
         <f>_xlfn.LET(
@@ -19073,37 +18983,33 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="J242" s="11"/>
       <c r="K242" s="11"/>
       <c r="L242" s="9"/>
       <c r="M242" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K242="","",IF(L242="","参照先未定義",_xlfn.XLOOKUP(L242,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N242" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(K242="","",IF(L242="","参照先未定義",_xlfn.XLOOKUP(L242,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N242" s="11"/>
       <c r="O242" s="11"/>
-      <c r="P242" s="11" t="s">
-        <v>115</v>
-      </c>
+      <c r="P242" s="11"/>
       <c r="Q242" s="11"/>
       <c r="R242" s="9"/>
       <c r="S242" s="9"/>
-      <c r="T242" s="9"/>
-      <c r="U242" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="243" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T242" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U242" s="11"/>
+    </row>
+    <row r="243" spans="1:21" ht="18.75" customHeight="1">
       <c r="A243" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B243" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>relation.soft_delete_flag</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.mutter</v>
       </c>
       <c r="C243" s="10">
         <f t="shared" si="6"/>
@@ -19111,22 +19017,22 @@
       </c>
       <c r="D243" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D243" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>relation</v>
+        <v>vtuber_profiles_lang</v>
       </c>
       <c r="E243" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E243" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>関係値</v>
+        <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="H243" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="I243" s="11">
+        <v>87</v>
+      </c>
+      <c r="I243" s="11" t="str">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H243,FIND("(",H243)+1,FIND(")",H243)-FIND("(",H243)-1),
     _xlfn.XLOOKUP(
@@ -19140,55 +19046,54 @@
         )
     )
 )</f>
-        <v>8</v>
+        <v>-</v>
       </c>
       <c r="J243" s="11"/>
       <c r="K243" s="11"/>
       <c r="L243" s="9"/>
       <c r="M243" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K243="","",IF(L243="","参照先未定義",_xlfn.XLOOKUP(L243,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N243" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(K243="","",IF(L243="","参照先未定義",_xlfn.XLOOKUP(L243,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N243" s="11"/>
       <c r="O243" s="11"/>
-      <c r="P243" s="11">
-        <v>0</v>
-      </c>
+      <c r="P243" s="11"/>
       <c r="Q243" s="11"/>
       <c r="R243" s="9"/>
       <c r="S243" s="9"/>
-      <c r="T243" s="9"/>
+      <c r="T243" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U243" s="11"/>
     </row>
-    <row r="244" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" ht="18.75" customHeight="1">
       <c r="A244" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B244" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>vtuber_profiles_lang.vtuber_profiles_lang_uuid</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.catchphrase</v>
       </c>
       <c r="C244" s="10">
         <f t="shared" si="6"/>
         <v>243</v>
       </c>
-      <c r="D244" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="E244" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="F244" s="11" t="str">
-        <f>D244&amp;"_uuid"</f>
-        <v>vtuber_profiles_lang_uuid</v>
+      <c r="D244" s="11" t="str" cm="1">
+        <f t="array" aca="1" ref="D244" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
+        <v>vtuber_profiles_lang</v>
+      </c>
+      <c r="E244" s="11" t="str" cm="1">
+        <f t="array" aca="1" ref="E244" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
+        <v>Vtuberプロフィール(各言語)</v>
+      </c>
+      <c r="F244" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="H244" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I244" s="11">
         <f>_xlfn.LET(
@@ -19204,39 +19109,33 @@
         )
     )
 )</f>
-        <v>128</v>
-      </c>
-      <c r="J244" s="11" t="s">
-        <v>475</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="J244" s="11"/>
       <c r="K244" s="11"/>
       <c r="L244" s="9"/>
       <c r="M244" s="11" t="str">
-        <f>_xlfn.SINGLE(IF(K244="","",IF(L244="","参照先未定義",_xlfn.XLOOKUP(L244,B:B,C:C,"エラー"))))</f>
-        <v/>
-      </c>
-      <c r="N244" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="O244" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="P244" s="11" t="s">
-        <v>52</v>
-      </c>
+        <f>IF(K244="","",IF(L244="","参照先未定義",_xlfn.XLOOKUP(L244,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N244" s="11"/>
+      <c r="O244" s="11"/>
+      <c r="P244" s="11"/>
       <c r="Q244" s="11"/>
       <c r="R244" s="9"/>
       <c r="S244" s="9"/>
-      <c r="T244" s="9"/>
+      <c r="T244" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U244" s="11"/>
     </row>
-    <row r="245" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" ht="18.75" customHeight="1">
       <c r="A245" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B245" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>vtuber_profiles_lang.vtuber_profiles_id</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.favorite</v>
       </c>
       <c r="C245" s="10">
         <f t="shared" si="6"/>
@@ -19251,13 +19150,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="H245" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I245" s="11">
         <f>_xlfn.LET(
@@ -19273,44 +19172,36 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="J245" s="11"/>
-      <c r="K245" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="L245" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="M245" s="11">
-        <f>_xlfn.SINGLE(IF(K245="","",IF(L245="","参照先未定義",_xlfn.XLOOKUP(L245,B:B,C:C,"エラー"))))</f>
-        <v>1</v>
-      </c>
-      <c r="N245" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O245" s="11" t="s">
-        <v>484</v>
-      </c>
+      <c r="K245" s="11"/>
+      <c r="L245" s="9"/>
+      <c r="M245" s="11" t="str">
+        <f>IF(K245="","",IF(L245="","参照先未定義",_xlfn.XLOOKUP(L245,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N245" s="11"/>
+      <c r="O245" s="11"/>
       <c r="P245" s="11"/>
-      <c r="Q245" s="11" t="s">
-        <v>487</v>
-      </c>
+      <c r="Q245" s="11"/>
       <c r="R245" s="9"/>
       <c r="S245" s="9"/>
-      <c r="T245" s="9"/>
+      <c r="T245" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U245" s="11"/>
     </row>
-    <row r="246" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" ht="18.75" customHeight="1">
       <c r="A246" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B246" s="9" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>vtuber_profiles_lang.lang</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.dis_favorite</v>
       </c>
       <c r="C246" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="C246:C266" si="8">ROW()-1</f>
         <v>245</v>
       </c>
       <c r="D246" s="11" t="str" cm="1">
@@ -19322,13 +19213,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>466</v>
+        <v>92</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>465</v>
+        <v>93</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I246" s="11">
         <f>_xlfn.LET(
@@ -19344,44 +19235,36 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="J246" s="11"/>
-      <c r="K246" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="L246" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="M246" s="11">
-        <f ca="1">IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
-        <v>102</v>
-      </c>
-      <c r="N246" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O246" s="11" t="s">
-        <v>484</v>
-      </c>
+      <c r="K246" s="11"/>
+      <c r="L246" s="9"/>
+      <c r="M246" s="11" t="str">
+        <f>IF(K246="","",IF(L246="","参照先未定義",_xlfn.XLOOKUP(L246,B:B,C:C,"エラー")))</f>
+        <v/>
+      </c>
+      <c r="N246" s="11"/>
+      <c r="O246" s="11"/>
       <c r="P246" s="11"/>
-      <c r="Q246" s="11" t="s">
-        <v>487</v>
-      </c>
+      <c r="Q246" s="11"/>
       <c r="R246" s="9"/>
       <c r="S246" s="9"/>
-      <c r="T246" s="9"/>
+      <c r="T246" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U246" s="11"/>
     </row>
-    <row r="247" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" ht="18.75" customHeight="1">
       <c r="A247" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B247" s="9" t="str">
-        <f t="shared" ref="B247:B275" ca="1" si="7">D247&amp;"."&amp;F247</f>
-        <v>vtuber_profiles_lang.name</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>vtuber_profiles_lang.hobby</v>
       </c>
       <c r="C247" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>246</v>
       </c>
       <c r="D247" s="11" t="str" cm="1">
@@ -19393,13 +19276,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="H247" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I247" s="11">
         <f>_xlfn.LET(
@@ -19415,7 +19298,7 @@
         )
     )
 )</f>
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="J247" s="11"/>
       <c r="K247" s="11"/>
@@ -19424,31 +19307,27 @@
         <f>IF(K247="","",IF(L247="","参照先未定義",_xlfn.XLOOKUP(L247,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N247" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="N247" s="11"/>
       <c r="O247" s="11"/>
       <c r="P247" s="11"/>
       <c r="Q247" s="11"/>
-      <c r="R247" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="R247" s="9"/>
       <c r="S247" s="9"/>
       <c r="T247" s="9" t="s">
         <v>51</v>
       </c>
       <c r="U247" s="11"/>
     </row>
-    <row r="248" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" ht="18.75" customHeight="1">
       <c r="A248" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B248" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.nickname</v>
+        <v>vtuber_profiles_lang.dream</v>
       </c>
       <c r="C248" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>247</v>
       </c>
       <c r="D248" s="11" t="str" cm="1">
@@ -19460,13 +19339,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I248" s="11">
         <f>_xlfn.LET(
@@ -19482,7 +19361,7 @@
         )
     )
 )</f>
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="J248" s="11"/>
       <c r="K248" s="11"/>
@@ -19502,16 +19381,16 @@
       </c>
       <c r="U248" s="11"/>
     </row>
-    <row r="249" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" ht="18.75" customHeight="1">
       <c r="A249" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B249" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.birthday</v>
+        <v>vtuber_profiles_lang.messages</v>
       </c>
       <c r="C249" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>248</v>
       </c>
       <c r="D249" s="11" t="str" cm="1">
@@ -19523,15 +19402,15 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H249" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I249" s="11">
+        <v>87</v>
+      </c>
+      <c r="I249" s="11" t="str">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H249,FIND("(",H249)+1,FIND(")",H249)-FIND("(",H249)-1),
     _xlfn.XLOOKUP(
@@ -19545,7 +19424,7 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>-</v>
       </c>
       <c r="J249" s="11"/>
       <c r="K249" s="11"/>
@@ -19565,16 +19444,16 @@
       </c>
       <c r="U249" s="11"/>
     </row>
-    <row r="250" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" ht="18.75" customHeight="1">
       <c r="A250" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B250" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.blood_type</v>
+        <v>vtuber_profiles_lang.profile_detail</v>
       </c>
       <c r="C250" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>249</v>
       </c>
       <c r="D250" s="11" t="str" cm="1">
@@ -19586,15 +19465,15 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="H250" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="I250" s="11">
+        <v>87</v>
+      </c>
+      <c r="I250" s="11" t="str">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H250,FIND("(",H250)+1,FIND(")",H250)-FIND("(",H250)-1),
     _xlfn.XLOOKUP(
@@ -19608,7 +19487,7 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>-</v>
       </c>
       <c r="J250" s="11"/>
       <c r="K250" s="11"/>
@@ -19626,18 +19505,20 @@
       <c r="T250" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="U250" s="11"/>
-    </row>
-    <row r="251" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U250" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21" ht="18.75" customHeight="1">
       <c r="A251" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B251" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.height</v>
+        <v>vtuber_profiles_lang.create_datetime</v>
       </c>
       <c r="C251" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="D251" s="11" t="str" cm="1">
@@ -19649,13 +19530,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="H251" s="11" t="s">
-        <v>77</v>
+        <v>492</v>
       </c>
       <c r="I251" s="11">
         <f>_xlfn.LET(
@@ -19671,7 +19552,7 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J251" s="11"/>
       <c r="K251" s="11"/>
@@ -19680,27 +19561,29 @@
         <f>IF(K251="","",IF(L251="","参照先未定義",_xlfn.XLOOKUP(L251,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N251" s="11"/>
+      <c r="N251" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O251" s="11"/>
-      <c r="P251" s="11"/>
+      <c r="P251" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="Q251" s="11"/>
       <c r="R251" s="9"/>
       <c r="S251" s="9"/>
-      <c r="T251" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T251" s="9"/>
       <c r="U251" s="11"/>
     </row>
-    <row r="252" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" ht="18.75" customHeight="1">
       <c r="A252" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B252" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.mutter</v>
+        <v>vtuber_profiles_lang.create_user</v>
       </c>
       <c r="C252" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>251</v>
       </c>
       <c r="D252" s="11" t="str" cm="1">
@@ -19712,15 +19595,15 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H252" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I252" s="11" t="str">
+        <v>71</v>
+      </c>
+      <c r="I252" s="11">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H252,FIND("(",H252)+1,FIND(")",H252)-FIND("(",H252)-1),
     _xlfn.XLOOKUP(
@@ -19734,7 +19617,7 @@
         )
     )
 )</f>
-        <v>-</v>
+        <v>256</v>
       </c>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
@@ -19743,27 +19626,31 @@
         <f>IF(K252="","",IF(L252="","参照先未定義",_xlfn.XLOOKUP(L252,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N252" s="11"/>
+      <c r="N252" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O252" s="11"/>
-      <c r="P252" s="11"/>
+      <c r="P252" s="11" t="s">
+        <v>115</v>
+      </c>
       <c r="Q252" s="11"/>
       <c r="R252" s="9"/>
       <c r="S252" s="9"/>
-      <c r="T252" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U252" s="11"/>
-    </row>
-    <row r="253" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T252" s="9"/>
+      <c r="U252" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21" ht="18.75" customHeight="1">
       <c r="A253" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B253" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.catchphrase</v>
+        <v>vtuber_profiles_lang.update_datetime</v>
       </c>
       <c r="C253" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>252</v>
       </c>
       <c r="D253" s="11" t="str" cm="1">
@@ -19775,13 +19662,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="H253" s="11" t="s">
-        <v>68</v>
+        <v>492</v>
       </c>
       <c r="I253" s="11">
         <f>_xlfn.LET(
@@ -19797,7 +19684,7 @@
         )
     )
 )</f>
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="J253" s="11"/>
       <c r="K253" s="11"/>
@@ -19806,27 +19693,29 @@
         <f>IF(K253="","",IF(L253="","参照先未定義",_xlfn.XLOOKUP(L253,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N253" s="11"/>
+      <c r="N253" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O253" s="11"/>
-      <c r="P253" s="11"/>
+      <c r="P253" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="Q253" s="11"/>
       <c r="R253" s="9"/>
       <c r="S253" s="9"/>
-      <c r="T253" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T253" s="9"/>
       <c r="U253" s="11"/>
     </row>
-    <row r="254" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" ht="18.75" customHeight="1">
       <c r="A254" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B254" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.favorite</v>
+        <v>vtuber_profiles_lang.update_user</v>
       </c>
       <c r="C254" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>253</v>
       </c>
       <c r="D254" s="11" t="str" cm="1">
@@ -19838,13 +19727,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F254" s="11" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G254" s="11" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="H254" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I254" s="11">
         <f>_xlfn.LET(
@@ -19860,7 +19749,7 @@
         )
     )
 )</f>
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="J254" s="11"/>
       <c r="K254" s="11"/>
@@ -19869,27 +19758,31 @@
         <f>IF(K254="","",IF(L254="","参照先未定義",_xlfn.XLOOKUP(L254,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N254" s="11"/>
+      <c r="N254" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O254" s="11"/>
-      <c r="P254" s="11"/>
+      <c r="P254" s="11" t="s">
+        <v>115</v>
+      </c>
       <c r="Q254" s="11"/>
       <c r="R254" s="9"/>
       <c r="S254" s="9"/>
-      <c r="T254" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U254" s="11"/>
-    </row>
-    <row r="255" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T254" s="9"/>
+      <c r="U254" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21" ht="18">
       <c r="A255" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B255" s="9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.dis_favorite</v>
+        <v>vtuber_profiles_lang.soft_delete_flag</v>
       </c>
       <c r="C255" s="10">
-        <f t="shared" ref="C255:C275" si="8">ROW()-1</f>
+        <f t="shared" si="8"/>
         <v>254</v>
       </c>
       <c r="D255" s="11" t="str" cm="1">
@@ -19901,13 +19794,13 @@
         <v>Vtuberプロフィール(各言語)</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="H255" s="11" t="s">
-        <v>68</v>
+        <v>494</v>
       </c>
       <c r="I255" s="11">
         <f>_xlfn.LET(
@@ -19923,7 +19816,7 @@
         )
     )
 )</f>
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="J255" s="11"/>
       <c r="K255" s="11"/>
@@ -19932,45 +19825,46 @@
         <f>IF(K255="","",IF(L255="","参照先未定義",_xlfn.XLOOKUP(L255,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N255" s="11"/>
+      <c r="N255" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O255" s="11"/>
-      <c r="P255" s="11"/>
+      <c r="P255" s="11">
+        <v>0</v>
+      </c>
       <c r="Q255" s="11"/>
       <c r="R255" s="9"/>
       <c r="S255" s="9"/>
-      <c r="T255" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T255" s="9"/>
       <c r="U255" s="11"/>
     </row>
-    <row r="256" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" ht="18">
       <c r="A256" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B256" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.hobby</v>
+        <f t="shared" ref="B256:B258" si="9">D256&amp;"."&amp;F256</f>
+        <v>profile_tag.profile_tag_uuid</v>
       </c>
       <c r="C256" s="10">
         <f t="shared" si="8"/>
         <v>255</v>
       </c>
-      <c r="D256" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D256" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
-      </c>
-      <c r="E256" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E256" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
-      </c>
-      <c r="F256" s="11" t="s">
-        <v>94</v>
+      <c r="D256" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="E256" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="F256" s="11" t="str">
+        <f>D256&amp;"_uuid"</f>
+        <v>profile_tag_uuid</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="H256" s="11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I256" s="11">
         <f>_xlfn.LET(
@@ -19986,33 +19880,39 @@
         )
     )
 )</f>
-        <v>512</v>
-      </c>
-      <c r="J256" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="J256" s="11" t="s">
+        <v>465</v>
+      </c>
       <c r="K256" s="11"/>
       <c r="L256" s="9"/>
       <c r="M256" s="11" t="str">
         <f>IF(K256="","",IF(L256="","参照先未定義",_xlfn.XLOOKUP(L256,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N256" s="11"/>
-      <c r="O256" s="11"/>
-      <c r="P256" s="11"/>
+      <c r="N256" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="O256" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="P256" s="11" t="s">
+        <v>52</v>
+      </c>
       <c r="Q256" s="11"/>
       <c r="R256" s="9"/>
       <c r="S256" s="9"/>
-      <c r="T256" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T256" s="9"/>
       <c r="U256" s="11"/>
     </row>
-    <row r="257" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" ht="18">
       <c r="A257" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B257" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.dream</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>profile_tag.vtuber_profiles_id</v>
       </c>
       <c r="C257" s="10">
         <f t="shared" si="8"/>
@@ -20020,20 +19920,20 @@
       </c>
       <c r="D257" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D257" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E257" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E257" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>96</v>
+        <v>470</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="H257" s="11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I257" s="11">
         <f>_xlfn.LET(
@@ -20049,33 +19949,41 @@
         )
     )
 )</f>
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="J257" s="11"/>
-      <c r="K257" s="11"/>
-      <c r="L257" s="9"/>
-      <c r="M257" s="11" t="str">
+      <c r="K257" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L257" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="M257" s="11">
         <f>IF(K257="","",IF(L257="","参照先未定義",_xlfn.XLOOKUP(L257,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N257" s="11"/>
-      <c r="O257" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="N257" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O257" s="11" t="s">
+        <v>475</v>
+      </c>
       <c r="P257" s="11"/>
-      <c r="Q257" s="11"/>
+      <c r="Q257" s="11" t="s">
+        <v>472</v>
+      </c>
       <c r="R257" s="9"/>
       <c r="S257" s="9"/>
-      <c r="T257" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T257" s="9"/>
       <c r="U257" s="11"/>
     </row>
-    <row r="258" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" ht="18">
       <c r="A258" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B258" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.messages</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>profile_tag.tag</v>
       </c>
       <c r="C258" s="10">
         <f t="shared" si="8"/>
@@ -20083,22 +19991,22 @@
       </c>
       <c r="D258" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D258" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E258" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E258" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>98</v>
+        <v>471</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="H258" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I258" s="11" t="str">
+        <v>49</v>
+      </c>
+      <c r="I258" s="11">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H258,FIND("(",H258)+1,FIND(")",H258)-FIND("(",H258)-1),
     _xlfn.XLOOKUP(
@@ -20112,19 +20020,29 @@
         )
     )
 )</f>
-        <v>-</v>
+        <v>128</v>
       </c>
       <c r="J258" s="11"/>
-      <c r="K258" s="11"/>
-      <c r="L258" s="9"/>
-      <c r="M258" s="11" t="str">
-        <f>IF(K258="","",IF(L258="","参照先未定義",_xlfn.XLOOKUP(L258,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N258" s="11"/>
-      <c r="O258" s="11"/>
+      <c r="K258" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="L258" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="M258" s="11">
+        <f ca="1">IF(K258="","",IF(L258="","参照先未定義",_xlfn.XLOOKUP(L258,B:B,C:C,"エラー")))</f>
+        <v>21</v>
+      </c>
+      <c r="N258" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O258" s="11" t="s">
+        <v>475</v>
+      </c>
       <c r="P258" s="11"/>
-      <c r="Q258" s="11"/>
+      <c r="Q258" s="11" t="s">
+        <v>472</v>
+      </c>
       <c r="R258" s="9"/>
       <c r="S258" s="9"/>
       <c r="T258" s="9" t="s">
@@ -20132,36 +20050,36 @@
       </c>
       <c r="U258" s="11"/>
     </row>
-    <row r="259" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" ht="18">
       <c r="A259" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B259" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.profile_detail</v>
+        <f ca="1">D259&amp;"."&amp;F259</f>
+        <v>profile_tag.create_datetime</v>
       </c>
       <c r="C259" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>258</v>
       </c>
       <c r="D259" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D259" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E259" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E259" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H259" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I259" s="11" t="str">
+        <v>492</v>
+      </c>
+      <c r="I259" s="11">
         <f>_xlfn.LET(
     _xlpm.可変bit数,--MID(H259,FIND("(",H259)+1,FIND(")",H259)-FIND("(",H259)-1),
     _xlfn.XLOOKUP(
@@ -20175,7 +20093,7 @@
         )
     )
 )</f>
-        <v>-</v>
+        <v>64</v>
       </c>
       <c r="J259" s="11"/>
       <c r="K259" s="11"/>
@@ -20184,47 +20102,47 @@
         <f>IF(K259="","",IF(L259="","参照先未定義",_xlfn.XLOOKUP(L259,B:B,C:C,"エラー")))</f>
         <v/>
       </c>
-      <c r="N259" s="11"/>
+      <c r="N259" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="O259" s="11"/>
-      <c r="P259" s="11"/>
+      <c r="P259" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="Q259" s="11"/>
       <c r="R259" s="9"/>
       <c r="S259" s="9"/>
-      <c r="T259" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U259" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="260" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T259" s="9"/>
+      <c r="U259" s="11"/>
+    </row>
+    <row r="260" spans="1:21" ht="18.75" customHeight="1">
       <c r="A260" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B260" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.create_datetime</v>
+        <f ca="1">D260&amp;"."&amp;F260</f>
+        <v>profile_tag.create_user</v>
       </c>
       <c r="C260" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>259</v>
       </c>
       <c r="D260" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D260" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E260" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E260" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H260" s="11" t="s">
-        <v>502</v>
+        <v>71</v>
       </c>
       <c r="I260" s="11">
         <f>_xlfn.LET(
@@ -20240,7 +20158,7 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
@@ -20254,42 +20172,44 @@
       </c>
       <c r="O260" s="11"/>
       <c r="P260" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q260" s="11"/>
       <c r="R260" s="9"/>
       <c r="S260" s="9"/>
       <c r="T260" s="9"/>
-      <c r="U260" s="11"/>
-    </row>
-    <row r="261" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U260" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21" ht="18.75" customHeight="1">
       <c r="A261" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B261" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.create_user</v>
+        <f ca="1">D261&amp;"."&amp;F261</f>
+        <v>profile_tag.update_datetime</v>
       </c>
       <c r="C261" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>260</v>
       </c>
       <c r="D261" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D261" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E261" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E261" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H261" s="11" t="s">
-        <v>71</v>
+        <v>492</v>
       </c>
       <c r="I261" s="11">
         <f>_xlfn.LET(
@@ -20305,7 +20225,7 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="J261" s="11"/>
       <c r="K261" s="11"/>
@@ -20319,44 +20239,42 @@
       </c>
       <c r="O261" s="11"/>
       <c r="P261" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q261" s="11"/>
       <c r="R261" s="9"/>
       <c r="S261" s="9"/>
       <c r="T261" s="9"/>
-      <c r="U261" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="262" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U261" s="11"/>
+    </row>
+    <row r="262" spans="1:21" ht="18.75" customHeight="1">
       <c r="A262" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B262" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.update_datetime</v>
+        <f ca="1">D262&amp;"."&amp;F262</f>
+        <v>profile_tag.update_user</v>
       </c>
       <c r="C262" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>261</v>
       </c>
       <c r="D262" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D262" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E262" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E262" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H262" s="11" t="s">
-        <v>502</v>
+        <v>71</v>
       </c>
       <c r="I262" s="11">
         <f>_xlfn.LET(
@@ -20372,7 +20290,7 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J262" s="11"/>
       <c r="K262" s="11"/>
@@ -20386,42 +20304,44 @@
       </c>
       <c r="O262" s="11"/>
       <c r="P262" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q262" s="11"/>
       <c r="R262" s="9"/>
       <c r="S262" s="9"/>
       <c r="T262" s="9"/>
-      <c r="U262" s="11"/>
-    </row>
-    <row r="263" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U262" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21" ht="18.75" customHeight="1">
       <c r="A263" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B263" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.update_user</v>
+        <f ca="1">D263&amp;"."&amp;F263</f>
+        <v>profile_tag.soft_delete_flag</v>
       </c>
       <c r="C263" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>262</v>
       </c>
       <c r="D263" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D263" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
+        <v>profile_tag</v>
       </c>
       <c r="E263" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E263" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
+        <v>プロフィールのタグ</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H263" s="11" t="s">
-        <v>71</v>
+        <v>494</v>
       </c>
       <c r="I263" s="11">
         <f>_xlfn.LET(
@@ -20437,7 +20357,7 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="J263" s="11"/>
       <c r="K263" s="11"/>
@@ -20450,45 +20370,42 @@
         <v>51</v>
       </c>
       <c r="O263" s="11"/>
-      <c r="P263" s="11" t="s">
-        <v>115</v>
+      <c r="P263" s="11">
+        <v>0</v>
       </c>
       <c r="Q263" s="11"/>
       <c r="R263" s="9"/>
       <c r="S263" s="9"/>
       <c r="T263" s="9"/>
-      <c r="U263" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="264" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="U263" s="11"/>
+    </row>
+    <row r="264" spans="1:21" ht="18">
       <c r="A264" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B264" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>vtuber_profiles_lang.soft_delete_flag</v>
+        <f t="shared" si="7"/>
+        <v>profile_activity.profile_activity_uuid</v>
       </c>
       <c r="C264" s="10">
         <f t="shared" si="8"/>
         <v>263</v>
       </c>
-      <c r="D264" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D264" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>vtuber_profiles_lang</v>
-      </c>
-      <c r="E264" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E264" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>Vtuberプロフィール(各言語)</v>
-      </c>
-      <c r="F264" s="11" t="s">
-        <v>121</v>
+      <c r="D264" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="E264" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="F264" s="11" t="str">
+        <f>D264&amp;"_uuid"</f>
+        <v>profile_activity_uuid</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="H264" s="11" t="s">
-        <v>504</v>
+        <v>49</v>
       </c>
       <c r="I264" s="11">
         <f>_xlfn.LET(
@@ -20504,9 +20421,11 @@
         )
     )
 )</f>
-        <v>8</v>
-      </c>
-      <c r="J264" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="J264" s="11" t="s">
+        <v>465</v>
+      </c>
       <c r="K264" s="11"/>
       <c r="L264" s="9"/>
       <c r="M264" s="11" t="str">
@@ -20514,11 +20433,13 @@
         <v/>
       </c>
       <c r="N264" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O264" s="11"/>
-      <c r="P264" s="11">
-        <v>0</v>
+        <v>476</v>
+      </c>
+      <c r="O264" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="P264" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="Q264" s="11"/>
       <c r="R264" s="9"/>
@@ -20526,30 +20447,31 @@
       <c r="T264" s="9"/>
       <c r="U264" s="11"/>
     </row>
-    <row r="265" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" ht="18">
       <c r="A265" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B265" s="9" t="str">
-        <f t="shared" ref="B265:B267" si="9">D265&amp;"."&amp;F265</f>
-        <v>profile_tag.profile_tag_uuid</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>profile_activity.vtuber_profiles_id</v>
       </c>
       <c r="C265" s="10">
         <f t="shared" si="8"/>
         <v>264</v>
       </c>
-      <c r="D265" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="E265" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="F265" s="11" t="str">
-        <f>D265&amp;"_uuid"</f>
-        <v>profile_tag_uuid</v>
+      <c r="D265" s="11" t="str" cm="1">
+        <f t="array" aca="1" ref="D265" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
+        <v>profile_activity</v>
+      </c>
+      <c r="E265" s="11" t="str" cm="1">
+        <f t="array" aca="1" ref="E265" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
+        <v>プロフィールの活動ジャンル</v>
+      </c>
+      <c r="F265" s="11" t="s">
+        <v>470</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H265" s="11" t="s">
         <v>49</v>
@@ -20570,37 +20492,39 @@
 )</f>
         <v>128</v>
       </c>
-      <c r="J265" s="11" t="s">
+      <c r="J265" s="11"/>
+      <c r="K265" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L265" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="M265" s="11">
+        <f>IF(K265="","",IF(L265="","参照先未定義",_xlfn.XLOOKUP(L265,B:B,C:C,"エラー")))</f>
+        <v>1</v>
+      </c>
+      <c r="N265" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O265" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="K265" s="11"/>
-      <c r="L265" s="9"/>
-      <c r="M265" s="11" t="str">
-        <f>IF(K265="","",IF(L265="","参照先未定義",_xlfn.XLOOKUP(L265,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N265" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="O265" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="P265" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q265" s="11"/>
+      <c r="P265" s="11"/>
+      <c r="Q265" s="11" t="s">
+        <v>489</v>
+      </c>
       <c r="R265" s="9"/>
       <c r="S265" s="9"/>
       <c r="T265" s="9"/>
       <c r="U265" s="11"/>
     </row>
-    <row r="266" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" ht="18">
       <c r="A266" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B266" s="9" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>profile_tag.vtuber_profiles_id</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>profile_activity.activity</v>
       </c>
       <c r="C266" s="10">
         <f t="shared" si="8"/>
@@ -20608,20 +20532,20 @@
       </c>
       <c r="D266" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D266" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E266" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E266" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="H266" s="11" t="s">
-        <v>49</v>
+        <v>487</v>
       </c>
       <c r="I266" s="11">
         <f>_xlfn.LET(
@@ -20640,59 +20564,57 @@
         <v>128</v>
       </c>
       <c r="J266" s="11"/>
-      <c r="K266" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L266" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="M266" s="11">
+      <c r="K266" s="11"/>
+      <c r="L266" s="9"/>
+      <c r="M266" s="11" t="str">
         <f>IF(K266="","",IF(L266="","参照先未定義",_xlfn.XLOOKUP(L266,B:B,C:C,"エラー")))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="N266" s="11" t="s">
         <v>51</v>
       </c>
       <c r="O266" s="11" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="P266" s="11"/>
       <c r="Q266" s="11" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="R266" s="9"/>
       <c r="S266" s="9"/>
-      <c r="T266" s="9"/>
+      <c r="T266" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="U266" s="11"/>
     </row>
-    <row r="267" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" ht="18">
       <c r="A267" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B267" s="9" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v>profile_tag.tag</v>
+        <f ca="1">D267&amp;"."&amp;F267</f>
+        <v>profile_activity.create_datetime</v>
       </c>
       <c r="C267" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW()-1</f>
         <v>266</v>
       </c>
       <c r="D267" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D267" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E267" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E267" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>481</v>
+        <v>110</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="H267" s="11" t="s">
-        <v>49</v>
+        <v>492</v>
       </c>
       <c r="I267" s="11">
         <f>_xlfn.LET(
@@ -20708,43 +20630,35 @@
         )
     )
 )</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J267" s="11"/>
-      <c r="K267" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="L267" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="M267" s="11">
-        <f ca="1">IF(K267="","",IF(L267="","参照先未定義",_xlfn.XLOOKUP(L267,B:B,C:C,"エラー")))</f>
-        <v>21</v>
+      <c r="K267" s="11"/>
+      <c r="L267" s="9"/>
+      <c r="M267" s="11" t="str">
+        <f>IF(K267="","",IF(L267="","参照先未定義",_xlfn.XLOOKUP(L267,B:B,C:C,"エラー")))</f>
+        <v/>
       </c>
       <c r="N267" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="O267" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="P267" s="11"/>
-      <c r="Q267" s="11" t="s">
-        <v>482</v>
-      </c>
+      <c r="O267" s="11"/>
+      <c r="P267" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q267" s="11"/>
       <c r="R267" s="9"/>
       <c r="S267" s="9"/>
-      <c r="T267" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="T267" s="9"/>
       <c r="U267" s="11"/>
     </row>
-    <row r="268" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" ht="18.75" customHeight="1">
       <c r="A268" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B268" s="9" t="str">
         <f ca="1">D268&amp;"."&amp;F268</f>
-        <v>profile_tag.create_datetime</v>
+        <v>profile_activity.create_user</v>
       </c>
       <c r="C268" s="10">
         <f>ROW()-1</f>
@@ -20752,20 +20666,20 @@
       </c>
       <c r="D268" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D268" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E268" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E268" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H268" s="11" t="s">
-        <v>502</v>
+        <v>71</v>
       </c>
       <c r="I268" s="11">
         <f>_xlfn.LET(
@@ -20781,7 +20695,7 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
@@ -20795,21 +20709,23 @@
       </c>
       <c r="O268" s="11"/>
       <c r="P268" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q268" s="11"/>
       <c r="R268" s="9"/>
       <c r="S268" s="9"/>
       <c r="T268" s="9"/>
-      <c r="U268" s="11"/>
-    </row>
-    <row r="269" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U268" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21" ht="18.75" customHeight="1">
       <c r="A269" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B269" s="9" t="str">
         <f ca="1">D269&amp;"."&amp;F269</f>
-        <v>profile_tag.create_user</v>
+        <v>profile_activity.update_datetime</v>
       </c>
       <c r="C269" s="10">
         <f>ROW()-1</f>
@@ -20817,20 +20733,20 @@
       </c>
       <c r="D269" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D269" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E269" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E269" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H269" s="11" t="s">
-        <v>71</v>
+        <v>492</v>
       </c>
       <c r="I269" s="11">
         <f>_xlfn.LET(
@@ -20846,7 +20762,7 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="J269" s="11"/>
       <c r="K269" s="11"/>
@@ -20860,23 +20776,21 @@
       </c>
       <c r="O269" s="11"/>
       <c r="P269" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q269" s="11"/>
       <c r="R269" s="9"/>
       <c r="S269" s="9"/>
       <c r="T269" s="9"/>
-      <c r="U269" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="270" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U269" s="11"/>
+    </row>
+    <row r="270" spans="1:21" ht="18.75" customHeight="1">
       <c r="A270" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B270" s="9" t="str">
         <f ca="1">D270&amp;"."&amp;F270</f>
-        <v>profile_tag.update_datetime</v>
+        <v>profile_activity.update_user</v>
       </c>
       <c r="C270" s="10">
         <f>ROW()-1</f>
@@ -20884,20 +20798,20 @@
       </c>
       <c r="D270" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D270" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E270" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E270" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H270" s="11" t="s">
-        <v>502</v>
+        <v>71</v>
       </c>
       <c r="I270" s="11">
         <f>_xlfn.LET(
@@ -20913,7 +20827,7 @@
         )
     )
 )</f>
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="J270" s="11"/>
       <c r="K270" s="11"/>
@@ -20927,21 +20841,23 @@
       </c>
       <c r="O270" s="11"/>
       <c r="P270" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q270" s="11"/>
       <c r="R270" s="9"/>
       <c r="S270" s="9"/>
       <c r="T270" s="9"/>
-      <c r="U270" s="11"/>
-    </row>
-    <row r="271" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U270" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" ht="18.75" customHeight="1">
       <c r="A271" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B271" s="9" t="str">
         <f ca="1">D271&amp;"."&amp;F271</f>
-        <v>profile_tag.update_user</v>
+        <v>profile_activity.soft_delete_flag</v>
       </c>
       <c r="C271" s="10">
         <f>ROW()-1</f>
@@ -20949,20 +20865,20 @@
       </c>
       <c r="D271" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="D271" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
+        <v>profile_activity</v>
       </c>
       <c r="E271" s="11" t="str" cm="1">
         <f t="array" aca="1" ref="E271" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
+        <v>プロフィールの活動ジャンル</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H271" s="11" t="s">
-        <v>71</v>
+        <v>494</v>
       </c>
       <c r="I271" s="11">
         <f>_xlfn.LET(
@@ -20978,7 +20894,7 @@
         )
     )
 )</f>
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="J271" s="11"/>
       <c r="K271" s="11"/>
@@ -20991,621 +20907,17 @@
         <v>51</v>
       </c>
       <c r="O271" s="11"/>
-      <c r="P271" s="11" t="s">
-        <v>115</v>
+      <c r="P271" s="11">
+        <v>0</v>
       </c>
       <c r="Q271" s="11"/>
       <c r="R271" s="9"/>
       <c r="S271" s="9"/>
       <c r="T271" s="9"/>
-      <c r="U271" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="272" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B272" s="9" t="str">
-        <f ca="1">D272&amp;"."&amp;F272</f>
-        <v>profile_tag.soft_delete_flag</v>
-      </c>
-      <c r="C272" s="10">
-        <f>ROW()-1</f>
-        <v>271</v>
-      </c>
-      <c r="D272" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D272" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_tag</v>
-      </c>
-      <c r="E272" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E272" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールのタグ</v>
-      </c>
-      <c r="F272" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G272" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H272" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="I272" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H272,FIND("(",H272)+1,FIND(")",H272)-FIND("(",H272)-1),
-    _xlfn.XLOOKUP(
-        $H272,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H272,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H272,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H272,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>8</v>
-      </c>
-      <c r="J272" s="11"/>
-      <c r="K272" s="11"/>
-      <c r="L272" s="9"/>
-      <c r="M272" s="11" t="str">
-        <f>IF(K272="","",IF(L272="","参照先未定義",_xlfn.XLOOKUP(L272,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N272" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O272" s="11"/>
-      <c r="P272" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q272" s="11"/>
-      <c r="R272" s="9"/>
-      <c r="S272" s="9"/>
-      <c r="T272" s="9"/>
-      <c r="U272" s="11"/>
-    </row>
-    <row r="273" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B273" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>profile_activity.profile_activity_uuid</v>
-      </c>
-      <c r="C273" s="10">
-        <f t="shared" si="8"/>
-        <v>272</v>
-      </c>
-      <c r="D273" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="E273" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="F273" s="11" t="str">
-        <f>D273&amp;"_uuid"</f>
-        <v>profile_activity_uuid</v>
-      </c>
-      <c r="G273" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H273" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I273" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H273,FIND("(",H273)+1,FIND(")",H273)-FIND("(",H273)-1),
-    _xlfn.XLOOKUP(
-        $H273,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H273,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H273,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H273,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>128</v>
-      </c>
-      <c r="J273" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="K273" s="11"/>
-      <c r="L273" s="9"/>
-      <c r="M273" s="11" t="str">
-        <f>IF(K273="","",IF(L273="","参照先未定義",_xlfn.XLOOKUP(L273,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N273" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="O273" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="P273" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q273" s="11"/>
-      <c r="R273" s="9"/>
-      <c r="S273" s="9"/>
-      <c r="T273" s="9"/>
-      <c r="U273" s="11"/>
-    </row>
-    <row r="274" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B274" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>profile_activity.vtuber_profiles_id</v>
-      </c>
-      <c r="C274" s="10">
-        <f t="shared" si="8"/>
-        <v>273</v>
-      </c>
-      <c r="D274" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D274" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E274" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E274" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F274" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="G274" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H274" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I274" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H274,FIND("(",H274)+1,FIND(")",H274)-FIND("(",H274)-1),
-    _xlfn.XLOOKUP(
-        $H274,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H274,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H274,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H274,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>128</v>
-      </c>
-      <c r="J274" s="11"/>
-      <c r="K274" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L274" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="M274" s="11">
-        <f>IF(K274="","",IF(L274="","参照先未定義",_xlfn.XLOOKUP(L274,B:B,C:C,"エラー")))</f>
-        <v>1</v>
-      </c>
-      <c r="N274" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O274" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="P274" s="11"/>
-      <c r="Q274" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="R274" s="9"/>
-      <c r="S274" s="9"/>
-      <c r="T274" s="9"/>
-      <c r="U274" s="11"/>
-    </row>
-    <row r="275" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A275" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B275" s="9" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v>profile_activity.activity</v>
-      </c>
-      <c r="C275" s="10">
-        <f t="shared" si="8"/>
-        <v>274</v>
-      </c>
-      <c r="D275" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D275" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E275" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E275" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F275" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="G275" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H275" s="11" t="s">
-        <v>497</v>
-      </c>
-      <c r="I275" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H275,FIND("(",H275)+1,FIND(")",H275)-FIND("(",H275)-1),
-    _xlfn.XLOOKUP(
-        $H275,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H275,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H275,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H275,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>128</v>
-      </c>
-      <c r="J275" s="11"/>
-      <c r="K275" s="11"/>
-      <c r="L275" s="9"/>
-      <c r="M275" s="11" t="str">
-        <f>IF(K275="","",IF(L275="","参照先未定義",_xlfn.XLOOKUP(L275,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N275" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O275" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="P275" s="11"/>
-      <c r="Q275" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="R275" s="9"/>
-      <c r="S275" s="9"/>
-      <c r="T275" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U275" s="11"/>
-    </row>
-    <row r="276" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A276" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B276" s="9" t="str">
-        <f ca="1">D276&amp;"."&amp;F276</f>
-        <v>profile_activity.create_datetime</v>
-      </c>
-      <c r="C276" s="10">
-        <f>ROW()-1</f>
-        <v>275</v>
-      </c>
-      <c r="D276" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D276" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E276" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E276" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F276" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G276" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H276" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="I276" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H276,FIND("(",H276)+1,FIND(")",H276)-FIND("(",H276)-1),
-    _xlfn.XLOOKUP(
-        $H276,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H276,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H276,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H276,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>64</v>
-      </c>
-      <c r="J276" s="11"/>
-      <c r="K276" s="11"/>
-      <c r="L276" s="9"/>
-      <c r="M276" s="11" t="str">
-        <f>IF(K276="","",IF(L276="","参照先未定義",_xlfn.XLOOKUP(L276,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N276" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O276" s="11"/>
-      <c r="P276" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q276" s="11"/>
-      <c r="R276" s="9"/>
-      <c r="S276" s="9"/>
-      <c r="T276" s="9"/>
-      <c r="U276" s="11"/>
-    </row>
-    <row r="277" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B277" s="9" t="str">
-        <f ca="1">D277&amp;"."&amp;F277</f>
-        <v>profile_activity.create_user</v>
-      </c>
-      <c r="C277" s="10">
-        <f>ROW()-1</f>
-        <v>276</v>
-      </c>
-      <c r="D277" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D277" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E277" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E277" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F277" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="G277" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H277" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I277" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H277,FIND("(",H277)+1,FIND(")",H277)-FIND("(",H277)-1),
-    _xlfn.XLOOKUP(
-        $H277,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H277,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H277,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H277,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>256</v>
-      </c>
-      <c r="J277" s="11"/>
-      <c r="K277" s="11"/>
-      <c r="L277" s="9"/>
-      <c r="M277" s="11" t="str">
-        <f>IF(K277="","",IF(L277="","参照先未定義",_xlfn.XLOOKUP(L277,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N277" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O277" s="11"/>
-      <c r="P277" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q277" s="11"/>
-      <c r="R277" s="9"/>
-      <c r="S277" s="9"/>
-      <c r="T277" s="9"/>
-      <c r="U277" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="278" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B278" s="9" t="str">
-        <f ca="1">D278&amp;"."&amp;F278</f>
-        <v>profile_activity.update_datetime</v>
-      </c>
-      <c r="C278" s="10">
-        <f>ROW()-1</f>
-        <v>277</v>
-      </c>
-      <c r="D278" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D278" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E278" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E278" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F278" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G278" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H278" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="I278" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H278,FIND("(",H278)+1,FIND(")",H278)-FIND("(",H278)-1),
-    _xlfn.XLOOKUP(
-        $H278,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H278,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H278,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H278,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>64</v>
-      </c>
-      <c r="J278" s="11"/>
-      <c r="K278" s="11"/>
-      <c r="L278" s="9"/>
-      <c r="M278" s="11" t="str">
-        <f>IF(K278="","",IF(L278="","参照先未定義",_xlfn.XLOOKUP(L278,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N278" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O278" s="11"/>
-      <c r="P278" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q278" s="11"/>
-      <c r="R278" s="9"/>
-      <c r="S278" s="9"/>
-      <c r="T278" s="9"/>
-      <c r="U278" s="11"/>
-    </row>
-    <row r="279" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B279" s="9" t="str">
-        <f ca="1">D279&amp;"."&amp;F279</f>
-        <v>profile_activity.update_user</v>
-      </c>
-      <c r="C279" s="10">
-        <f>ROW()-1</f>
-        <v>278</v>
-      </c>
-      <c r="D279" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D279" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E279" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E279" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F279" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G279" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="H279" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I279" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H279,FIND("(",H279)+1,FIND(")",H279)-FIND("(",H279)-1),
-    _xlfn.XLOOKUP(
-        $H279,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H279,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H279,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H279,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>256</v>
-      </c>
-      <c r="J279" s="11"/>
-      <c r="K279" s="11"/>
-      <c r="L279" s="9"/>
-      <c r="M279" s="11" t="str">
-        <f>IF(K279="","",IF(L279="","参照先未定義",_xlfn.XLOOKUP(L279,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N279" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O279" s="11"/>
-      <c r="P279" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q279" s="11"/>
-      <c r="R279" s="9"/>
-      <c r="S279" s="9"/>
-      <c r="T279" s="9"/>
-      <c r="U279" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="280" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B280" s="9" t="str">
-        <f ca="1">D280&amp;"."&amp;F280</f>
-        <v>profile_activity.soft_delete_flag</v>
-      </c>
-      <c r="C280" s="10">
-        <f>ROW()-1</f>
-        <v>279</v>
-      </c>
-      <c r="D280" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="D280" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>profile_activity</v>
-      </c>
-      <c r="E280" s="11" t="str" cm="1">
-        <f t="array" aca="1" ref="E280" ca="1">INDIRECT(ADDRESS(ROW()-1,COLUMN()))</f>
-        <v>プロフィールの活動ジャンル</v>
-      </c>
-      <c r="F280" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G280" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H280" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="I280" s="11">
-        <f>_xlfn.LET(
-    _xlpm.可変bit数,--MID(H280,FIND("(",H280)+1,FIND(")",H280)-FIND("(",H280)-1),
-    _xlfn.XLOOKUP(
-        $H280,
-        型とバイト数!$B$3:$B$54,
-        型とバイト数!$E$3:$E$54,
-        IF(LEFT($H280,7)="varchar",_xlpm.可変bit数*8,
-            IF(LEFT($H280,4)="char",_xlpm.可変bit数*8,
-                IF(LEFT($H280,3)="bit",_xlpm.可変bit数,"???")
-            )
-        )
-    )
-)</f>
-        <v>8</v>
-      </c>
-      <c r="J280" s="11"/>
-      <c r="K280" s="11"/>
-      <c r="L280" s="9"/>
-      <c r="M280" s="11" t="str">
-        <f>IF(K280="","",IF(L280="","参照先未定義",_xlfn.XLOOKUP(L280,B:B,C:C,"エラー")))</f>
-        <v/>
-      </c>
-      <c r="N280" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="O280" s="11"/>
-      <c r="P280" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q280" s="11"/>
-      <c r="R280" s="9"/>
-      <c r="S280" s="9"/>
-      <c r="T280" s="9"/>
-      <c r="U280" s="11"/>
+      <c r="U271" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U280" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:U271" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -21615,61 +20927,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="93.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="93.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:7" ht="18">
+      <c r="A1" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" ht="19">
+      <c r="A2" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19">
+      <c r="A3" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>288</v>
       </c>
       <c r="D3" s="13">
         <v>2</v>
@@ -21679,21 +20991,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19">
       <c r="A4" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D4" s="14">
         <v>4</v>
@@ -21703,21 +21015,21 @@
         <v>32</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19">
       <c r="A5" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D5" s="13">
         <v>8</v>
@@ -21727,21 +21039,21 @@
         <v>64</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19">
       <c r="A6" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>82</v>
@@ -21751,21 +21063,21 @@
         <v>-</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19">
       <c r="A7" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>82</v>
@@ -21775,21 +21087,21 @@
         <v>-</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19">
       <c r="A8" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D8" s="14">
         <v>4</v>
@@ -21799,21 +21111,21 @@
         <v>32</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19">
       <c r="A9" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D9" s="13">
         <v>8</v>
@@ -21823,21 +21135,21 @@
         <v>64</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19">
       <c r="A10" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D10" s="14">
         <v>2</v>
@@ -21847,21 +21159,21 @@
         <v>16</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19">
       <c r="A11" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>163</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D11" s="13">
         <v>4</v>
@@ -21871,21 +21183,21 @@
         <v>32</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19">
       <c r="A12" s="14" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>61</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D12" s="14">
         <v>8</v>
@@ -21895,21 +21207,21 @@
         <v>64</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19">
       <c r="A13" s="13" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D13" s="13">
         <v>8</v>
@@ -21919,21 +21231,21 @@
         <v>64</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19">
       <c r="A14" s="14" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>82</v>
@@ -21943,21 +21255,21 @@
         <v>-</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19">
       <c r="A15" s="13" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>82</v>
@@ -21967,21 +21279,21 @@
         <v>-</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19">
       <c r="A16" s="14" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>82</v>
@@ -21991,21 +21303,21 @@
         <v>-</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19">
       <c r="A17" s="13" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D17" s="13">
         <v>8</v>
@@ -22015,21 +21327,21 @@
         <v>64</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19">
       <c r="A18" s="14" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D18" s="14">
         <v>8</v>
@@ -22039,21 +21351,21 @@
         <v>64</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19">
       <c r="A19" s="17" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D19" s="17">
         <v>8</v>
@@ -22064,18 +21376,18 @@
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="17" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19">
       <c r="A20" s="17" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D20" s="17">
         <v>8</v>
@@ -22086,18 +21398,18 @@
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19">
       <c r="A21" s="13" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D21" s="13">
         <v>4</v>
@@ -22107,21 +21419,21 @@
         <v>32</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19">
       <c r="A22" s="14" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
@@ -22131,21 +21443,21 @@
         <v>64</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19">
       <c r="A23" s="13" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D23" s="13">
         <v>12</v>
@@ -22155,21 +21467,21 @@
         <v>96</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19">
       <c r="A24" s="14" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D24" s="14">
         <v>12</v>
@@ -22179,21 +21491,21 @@
         <v>96</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19">
       <c r="A25" s="13" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D25" s="13">
         <v>1</v>
@@ -22203,21 +21515,21 @@
         <v>8</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19">
       <c r="A26" s="14" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>82</v>
@@ -22227,21 +21539,21 @@
         <v>-</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19">
       <c r="A27" s="13" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>82</v>
@@ -22251,21 +21563,21 @@
         <v>-</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19">
       <c r="A28" s="14" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D28" s="14">
         <v>16</v>
@@ -22275,21 +21587,21 @@
         <v>128</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19">
       <c r="A29" s="13" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D29" s="13">
         <v>32</v>
@@ -22299,21 +21611,21 @@
         <v>256</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19">
       <c r="A30" s="14" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D30" s="14">
         <v>32</v>
@@ -22323,21 +21635,21 @@
         <v>256</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19">
       <c r="A31" s="13" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D31" s="13">
         <v>32</v>
@@ -22347,21 +21659,21 @@
         <v>256</v>
       </c>
       <c r="F31" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19">
+      <c r="A32" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>367</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>373</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>374</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>82</v>
@@ -22371,21 +21683,21 @@
         <v>-</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19">
       <c r="A33" s="13" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>82</v>
@@ -22395,21 +21707,21 @@
         <v>-</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19">
       <c r="A34" s="14" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>82</v>
@@ -22419,21 +21731,21 @@
         <v>-</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19">
       <c r="A35" s="13" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D35" s="13">
         <v>24</v>
@@ -22443,21 +21755,21 @@
         <v>192</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19">
       <c r="A36" s="14" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>82</v>
@@ -22467,21 +21779,21 @@
         <v>-</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19">
       <c r="A37" s="13" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>82</v>
@@ -22491,21 +21803,21 @@
         <v>-</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19">
       <c r="A38" s="14" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D38" s="14">
         <v>6</v>
@@ -22515,21 +21827,21 @@
         <v>48</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="19">
       <c r="A39" s="13" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>82</v>
@@ -22539,21 +21851,21 @@
         <v>-</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="19">
       <c r="A40" s="14" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>82</v>
@@ -22563,21 +21875,21 @@
         <v>-</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="19">
       <c r="A41" s="13" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>82</v>
@@ -22590,18 +21902,18 @@
         <v>82</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="19">
       <c r="A42" s="14" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>82</v>
@@ -22614,18 +21926,18 @@
         <v>82</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="19">
       <c r="A43" s="13" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D43" s="13">
         <v>4</v>
@@ -22638,18 +21950,18 @@
         <v>82</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="19">
       <c r="A44" s="14" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>82</v>
@@ -22659,21 +21971,21 @@
         <v>-</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="19">
       <c r="A45" s="13" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D45" s="13">
         <v>16</v>
@@ -22683,21 +21995,21 @@
         <v>128</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="19">
       <c r="A46" s="14" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>82</v>
@@ -22707,21 +22019,21 @@
         <v>-</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="19">
       <c r="A47" s="13" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>82</v>
@@ -22731,21 +22043,21 @@
         <v>-</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="19">
       <c r="A48" s="14" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>82</v>
@@ -22755,21 +22067,21 @@
         <v>-</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="19">
       <c r="A49" s="13" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>82</v>
@@ -22779,21 +22091,21 @@
         <v>-</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="19">
       <c r="A50" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>82</v>
@@ -22803,21 +22115,21 @@
         <v>-</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="19">
       <c r="A51" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>441</v>
-      </c>
       <c r="C51" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>82</v>
@@ -22827,21 +22139,21 @@
         <v>-</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="19">
       <c r="A52" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D52" s="14" t="s">
         <v>82</v>
@@ -22851,21 +22163,21 @@
         <v>-</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="19">
       <c r="A53" s="13" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>82</v>
@@ -22875,21 +22187,21 @@
         <v>-</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="19">
       <c r="A54" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>82</v>
@@ -22899,10 +22211,10 @@
         <v>-</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
